--- a/Assignments/All-Star-Data.xlsx
+++ b/Assignments/All-Star-Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/thejjserg/Documents/GitHub/basketball-analytics/Assignments/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBCF0F1E-D690-2441-95F5-E72F86BEB0BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{315C0727-A5E2-E14D-834A-AE79E9047489}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="49440" yWindow="620" windowWidth="19220" windowHeight="20980" xr2:uid="{3473C8AF-537D-9E44-9C2C-9151BBD57575}"/>
+    <workbookView xWindow="42540" yWindow="3560" windowWidth="30240" windowHeight="17660" xr2:uid="{3473C8AF-537D-9E44-9C2C-9151BBD57575}"/>
   </bookViews>
   <sheets>
     <sheet name="East Players 2025-26" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
     <sheet name="East Teams Opp Totals 2025-26" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'East Players 2025-26'!$A$1:$AF$44</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'East Players 2025-26'!$A$1:$AG$44</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="113">
   <si>
     <t>Player</t>
   </si>
@@ -377,6 +377,9 @@
   </si>
   <si>
     <t>IND</t>
+  </si>
+  <si>
+    <t>Second Fan Returns</t>
   </si>
 </sst>
 </file>
@@ -439,12 +442,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -779,4270 +783,4403 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C606AA21-296B-D248-87CD-1A67A00CACCB}">
-  <dimension ref="A1:AG44"/>
+  <dimension ref="A1:AH44"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="21.83203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="20" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.1640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="4.83203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="5.83203125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="6.33203125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="5.83203125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="7" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="7.6640625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="5.83203125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="7" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="7.6640625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="5.83203125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="7" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="7.6640625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="8.6640625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="5.6640625" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="6.83203125" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="7.5" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="7.33203125" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="7.1640625" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="7" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="6.83203125" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="7" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="7.1640625" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="5.83203125" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="6.83203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.83203125" style="5" customWidth="1"/>
+    <col min="3" max="3" width="17.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.1640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="4.83203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="5.83203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="5.83203125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="5.83203125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="7" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="5.83203125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="7" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="8.6640625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="5.6640625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="6.83203125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="7.5" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="7.1640625" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="7" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="6.83203125" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="7" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="7.1640625" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="5.83203125" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="6.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="C1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>89</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>62</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="X1" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="Z1" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="AA1" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="AA1" s="1" t="s">
+      <c r="AB1" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="AB1" s="1" t="s">
+      <c r="AC1" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="AC1" s="1" t="s">
+      <c r="AD1" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="AD1" s="1" t="s">
+      <c r="AE1" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="AE1" s="1" t="s">
+      <c r="AF1" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="AF1" s="1" t="s">
+      <c r="AG1" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="AG1" s="1"/>
+      <c r="AH1" s="1"/>
     </row>
-    <row r="2" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>4</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="5">
+        <v>1908978</v>
+      </c>
+      <c r="C2" t="s">
         <v>5</v>
       </c>
-      <c r="C2">
+      <c r="D2">
         <v>21</v>
       </c>
-      <c r="D2">
+      <c r="E2">
         <v>16</v>
       </c>
-      <c r="E2">
+      <c r="F2">
         <v>5</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="H2" s="2" t="s">
         <v>90</v>
-      </c>
-      <c r="H2" s="2">
-        <v>35</v>
       </c>
       <c r="I2" s="2">
         <v>35</v>
       </c>
-      <c r="J2" s="3">
+      <c r="J2" s="2">
+        <v>35</v>
+      </c>
+      <c r="K2" s="3">
         <v>39.700000000000003</v>
       </c>
-      <c r="K2" s="2">
+      <c r="L2" s="2">
         <v>10.8</v>
       </c>
-      <c r="L2" s="3">
+      <c r="M2" s="3">
         <v>22.6</v>
       </c>
-      <c r="M2" s="2">
+      <c r="N2" s="2">
         <v>0.47699999999999998</v>
       </c>
-      <c r="N2" s="2">
+      <c r="O2" s="2">
         <v>3.7</v>
       </c>
-      <c r="O2" s="2">
+      <c r="P2" s="2">
         <v>9.1999999999999993</v>
       </c>
-      <c r="P2" s="2">
+      <c r="Q2" s="2">
         <v>0.40200000000000002</v>
       </c>
-      <c r="Q2" s="2">
+      <c r="R2" s="2">
         <v>7.1</v>
       </c>
-      <c r="R2" s="2">
+      <c r="S2" s="2">
         <v>13.4</v>
       </c>
-      <c r="S2" s="2">
+      <c r="T2" s="2">
         <v>0.52800000000000002</v>
       </c>
-      <c r="T2" s="2">
+      <c r="U2" s="2">
         <v>0.55800000000000005</v>
       </c>
-      <c r="U2" s="2">
+      <c r="V2" s="2">
         <v>5.7</v>
       </c>
-      <c r="V2" s="2">
+      <c r="W2" s="2">
         <v>6.5</v>
       </c>
-      <c r="W2" s="2">
+      <c r="X2" s="2">
         <v>0.872</v>
       </c>
-      <c r="X2" s="2">
+      <c r="Y2" s="2">
         <v>0.2</v>
       </c>
-      <c r="Y2" s="2">
+      <c r="Z2" s="2">
         <v>4.3</v>
       </c>
-      <c r="Z2" s="2">
+      <c r="AA2" s="2">
         <v>4.5</v>
       </c>
-      <c r="AA2" s="2">
+      <c r="AB2" s="2">
         <v>6.8</v>
       </c>
-      <c r="AB2" s="2">
+      <c r="AC2" s="2">
         <v>1.9</v>
       </c>
-      <c r="AC2" s="2">
+      <c r="AD2" s="2">
         <v>0.9</v>
       </c>
-      <c r="AD2" s="2">
+      <c r="AE2" s="2">
         <v>2.6</v>
       </c>
-      <c r="AE2" s="2">
+      <c r="AF2" s="2">
         <v>2.2000000000000002</v>
       </c>
-      <c r="AF2" s="2">
+      <c r="AG2" s="2">
         <v>30.9</v>
       </c>
     </row>
-    <row r="3" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>6</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="5">
+        <v>1514259</v>
+      </c>
+      <c r="C3" t="s">
         <v>7</v>
       </c>
-      <c r="C3">
+      <c r="D3">
         <v>24</v>
       </c>
-      <c r="D3">
+      <c r="E3">
         <v>14</v>
       </c>
-      <c r="E3">
+      <c r="F3">
         <v>3</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="H3" s="2" t="s">
         <v>92</v>
-      </c>
-      <c r="H3" s="2">
-        <v>36</v>
       </c>
       <c r="I3" s="2">
         <v>36</v>
       </c>
       <c r="J3" s="2">
+        <v>36</v>
+      </c>
+      <c r="K3" s="2">
         <v>34.299999999999997</v>
       </c>
-      <c r="K3" s="2">
+      <c r="L3" s="2">
         <v>10.9</v>
       </c>
-      <c r="L3" s="2">
+      <c r="M3" s="2">
         <v>21.9</v>
       </c>
-      <c r="M3" s="2">
+      <c r="N3" s="2">
         <v>0.495</v>
       </c>
-      <c r="N3" s="2">
+      <c r="O3" s="2">
         <v>2.2000000000000002</v>
       </c>
-      <c r="O3" s="2">
+      <c r="P3" s="2">
         <v>5.8</v>
       </c>
-      <c r="P3" s="2">
+      <c r="Q3" s="2">
         <v>0.376</v>
       </c>
-      <c r="Q3" s="2">
+      <c r="R3" s="2">
         <v>8.6999999999999993</v>
       </c>
-      <c r="R3" s="3">
+      <c r="S3" s="3">
         <v>16.100000000000001</v>
       </c>
-      <c r="S3" s="2">
+      <c r="T3" s="2">
         <v>0.53800000000000003</v>
       </c>
-      <c r="T3" s="2">
+      <c r="U3" s="2">
         <v>0.54500000000000004</v>
       </c>
-      <c r="U3" s="2">
+      <c r="V3" s="2">
         <v>5.6</v>
       </c>
-      <c r="V3" s="2">
+      <c r="W3" s="2">
         <v>7.2</v>
       </c>
-      <c r="W3" s="2">
+      <c r="X3" s="2">
         <v>0.77900000000000003</v>
       </c>
-      <c r="X3" s="2">
+      <c r="Y3" s="2">
         <v>1.2</v>
       </c>
-      <c r="Y3" s="2">
+      <c r="Z3" s="2">
         <v>5.3</v>
       </c>
-      <c r="Z3" s="2">
+      <c r="AA3" s="2">
         <v>6.4</v>
       </c>
-      <c r="AA3" s="2">
+      <c r="AB3" s="2">
         <v>5</v>
       </c>
-      <c r="AB3" s="2">
+      <c r="AC3" s="2">
         <v>1</v>
       </c>
-      <c r="AC3" s="2">
+      <c r="AD3" s="2">
         <v>0.4</v>
       </c>
-      <c r="AD3" s="2">
+      <c r="AE3" s="2">
         <v>3.8</v>
       </c>
-      <c r="AE3" s="2">
+      <c r="AF3" s="2">
         <v>3.1</v>
       </c>
-      <c r="AF3" s="2">
+      <c r="AG3" s="2">
         <v>29.5</v>
       </c>
-      <c r="AG3" s="2"/>
+      <c r="AH3" s="2"/>
     </row>
-    <row r="4" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>8</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="5">
+        <v>1530237</v>
+      </c>
+      <c r="C4" t="s">
         <v>9</v>
       </c>
-      <c r="C4">
+      <c r="D4">
         <v>22</v>
       </c>
-      <c r="D4">
+      <c r="E4">
         <v>18</v>
       </c>
-      <c r="E4">
+      <c r="F4">
         <v>7</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="H4" s="2" t="s">
         <v>93</v>
-      </c>
-      <c r="H4" s="2">
-        <v>36</v>
       </c>
       <c r="I4" s="2">
         <v>36</v>
       </c>
       <c r="J4" s="2">
+        <v>36</v>
+      </c>
+      <c r="K4" s="2">
         <v>33.799999999999997</v>
       </c>
-      <c r="K4" s="2">
+      <c r="L4" s="2">
         <v>10.4</v>
       </c>
-      <c r="L4" s="2">
+      <c r="M4" s="2">
         <v>21</v>
       </c>
-      <c r="M4" s="2">
+      <c r="N4" s="2">
         <v>0.495</v>
       </c>
-      <c r="N4" s="2">
+      <c r="O4" s="2">
         <v>3.9</v>
       </c>
-      <c r="O4" s="2">
+      <c r="P4" s="2">
         <v>10</v>
       </c>
-      <c r="P4" s="2">
+      <c r="Q4" s="2">
         <v>0.38500000000000001</v>
       </c>
-      <c r="Q4" s="2">
+      <c r="R4" s="2">
         <v>6.5</v>
       </c>
-      <c r="R4" s="2">
+      <c r="S4" s="2">
         <v>11</v>
       </c>
-      <c r="S4" s="2">
+      <c r="T4" s="2">
         <v>0.59499999999999997</v>
       </c>
-      <c r="T4" s="2">
+      <c r="U4" s="2">
         <v>0.58699999999999997</v>
       </c>
-      <c r="U4" s="2">
+      <c r="V4" s="2">
         <v>5.0999999999999996</v>
       </c>
-      <c r="V4" s="2">
+      <c r="W4" s="2">
         <v>6.1</v>
       </c>
-      <c r="W4" s="2">
+      <c r="X4" s="2">
         <v>0.84</v>
       </c>
-      <c r="X4" s="2">
+      <c r="Y4" s="2">
         <v>0.9</v>
       </c>
-      <c r="Y4" s="2">
+      <c r="Z4" s="2">
         <v>3.9</v>
       </c>
-      <c r="Z4" s="2">
+      <c r="AA4" s="2">
         <v>4.7</v>
       </c>
-      <c r="AA4" s="2">
+      <c r="AB4" s="2">
         <v>5.6</v>
       </c>
-      <c r="AB4" s="2">
+      <c r="AC4" s="2">
         <v>1.5</v>
       </c>
-      <c r="AC4" s="2">
+      <c r="AD4" s="2">
         <v>0.3</v>
       </c>
-      <c r="AD4" s="2">
+      <c r="AE4" s="2">
         <v>3.1</v>
       </c>
-      <c r="AE4" s="2">
+      <c r="AF4" s="2">
         <v>2.6</v>
       </c>
-      <c r="AF4" s="2">
+      <c r="AG4" s="2">
         <v>29.8</v>
       </c>
     </row>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>10</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="5">
+        <v>2092284</v>
+      </c>
+      <c r="C5" t="s">
         <v>11</v>
       </c>
-      <c r="C5">
+      <c r="D5">
         <v>17</v>
       </c>
-      <c r="D5">
+      <c r="E5">
         <v>22</v>
       </c>
-      <c r="E5">
+      <c r="F5">
         <v>11</v>
       </c>
-      <c r="G5" s="2" t="s">
+      <c r="H5" s="2" t="s">
         <v>86</v>
-      </c>
-      <c r="H5" s="2">
-        <v>25</v>
       </c>
       <c r="I5" s="2">
         <v>25</v>
       </c>
       <c r="J5" s="2">
+        <v>25</v>
+      </c>
+      <c r="K5" s="2">
         <v>29.2</v>
       </c>
-      <c r="K5" s="2">
+      <c r="L5" s="2">
         <v>11.2</v>
       </c>
-      <c r="L5" s="2">
+      <c r="M5" s="2">
         <v>17.2</v>
       </c>
-      <c r="M5" s="2">
+      <c r="N5" s="2">
         <v>0.64700000000000002</v>
       </c>
-      <c r="N5" s="2">
+      <c r="O5" s="2">
         <v>0.6</v>
       </c>
-      <c r="O5" s="2">
+      <c r="P5" s="2">
         <v>1.4</v>
       </c>
-      <c r="P5" s="2">
+      <c r="Q5" s="2">
         <v>0.4</v>
       </c>
-      <c r="Q5" s="3">
+      <c r="R5" s="3">
         <v>10.6</v>
       </c>
-      <c r="R5" s="2">
+      <c r="S5" s="2">
         <v>15.8</v>
       </c>
-      <c r="S5" s="2">
+      <c r="T5" s="2">
         <v>0.66900000000000004</v>
       </c>
-      <c r="T5" s="2">
+      <c r="U5" s="2">
         <v>0.66400000000000003</v>
       </c>
-      <c r="U5" s="2">
+      <c r="V5" s="2">
         <v>6.4</v>
       </c>
-      <c r="V5" s="2">
+      <c r="W5" s="2">
         <v>9.6</v>
       </c>
-      <c r="W5" s="2">
+      <c r="X5" s="2">
         <v>0.66</v>
       </c>
-      <c r="X5" s="2">
+      <c r="Y5" s="2">
         <v>3</v>
       </c>
-      <c r="Y5" s="2">
+      <c r="Z5" s="2">
         <v>6.7</v>
       </c>
-      <c r="Z5" s="2">
+      <c r="AA5" s="2">
         <v>9.8000000000000007</v>
       </c>
-      <c r="AA5" s="2">
+      <c r="AB5" s="2">
         <v>5.7</v>
       </c>
-      <c r="AB5" s="2">
+      <c r="AC5" s="2">
         <v>0.9</v>
       </c>
-      <c r="AC5" s="2">
+      <c r="AD5" s="2">
         <v>0.8</v>
       </c>
-      <c r="AD5" s="2">
+      <c r="AE5" s="2">
         <v>3.2</v>
       </c>
-      <c r="AE5" s="2">
+      <c r="AF5" s="2">
         <v>2.7</v>
       </c>
-      <c r="AF5" s="2">
+      <c r="AG5" s="2">
         <v>29.2</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>12</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="5">
+        <v>1916497</v>
+      </c>
+      <c r="C6" t="s">
         <v>13</v>
       </c>
-      <c r="C6">
+      <c r="D6">
         <v>25</v>
       </c>
-      <c r="D6">
+      <c r="E6">
         <v>14</v>
       </c>
-      <c r="E6">
+      <c r="F6">
         <v>2</v>
       </c>
-      <c r="G6" s="2" t="s">
+      <c r="H6" s="2" t="s">
         <v>90</v>
-      </c>
-      <c r="H6" s="2">
-        <v>36</v>
       </c>
       <c r="I6" s="2">
         <v>36</v>
       </c>
       <c r="J6" s="2">
+        <v>36</v>
+      </c>
+      <c r="K6" s="2">
         <v>35.299999999999997</v>
       </c>
-      <c r="K6" s="2">
+      <c r="L6" s="2">
         <v>10.3</v>
       </c>
-      <c r="L6" s="2">
+      <c r="M6" s="2">
         <v>21.4</v>
       </c>
-      <c r="M6" s="2">
+      <c r="N6" s="2">
         <v>0.48099999999999998</v>
       </c>
-      <c r="N6" s="2">
+      <c r="O6" s="2">
         <v>3.1</v>
       </c>
-      <c r="O6" s="2">
+      <c r="P6" s="2">
         <v>7.9</v>
       </c>
-      <c r="P6" s="2">
+      <c r="Q6" s="2">
         <v>0.38900000000000001</v>
       </c>
-      <c r="Q6" s="2">
+      <c r="R6" s="2">
         <v>7.2</v>
       </c>
-      <c r="R6" s="2">
+      <c r="S6" s="2">
         <v>13.5</v>
       </c>
-      <c r="S6" s="2">
+      <c r="T6" s="2">
         <v>0.53400000000000003</v>
       </c>
-      <c r="T6" s="2">
+      <c r="U6" s="2">
         <v>0.55300000000000005</v>
       </c>
-      <c r="U6" s="2">
+      <c r="V6" s="2">
         <v>5.3</v>
       </c>
-      <c r="V6" s="2">
+      <c r="W6" s="2">
         <v>6.2</v>
       </c>
-      <c r="W6" s="2">
+      <c r="X6" s="2">
         <v>0.85199999999999998</v>
       </c>
-      <c r="X6" s="2">
+      <c r="Y6" s="2">
         <v>0.6</v>
       </c>
-      <c r="Y6" s="2">
+      <c r="Z6" s="2">
         <v>2.8</v>
       </c>
-      <c r="Z6" s="2">
+      <c r="AA6" s="2">
         <v>3.3</v>
       </c>
-      <c r="AA6" s="2">
+      <c r="AB6" s="2">
         <v>6.3</v>
       </c>
-      <c r="AB6" s="2">
+      <c r="AC6" s="2">
         <v>0.7</v>
       </c>
-      <c r="AC6" s="2">
+      <c r="AD6" s="2">
         <v>0.1</v>
       </c>
-      <c r="AD6" s="2">
+      <c r="AE6" s="2">
         <v>2.2999999999999998</v>
       </c>
-      <c r="AE6" s="2">
+      <c r="AF6" s="2">
         <v>2.5</v>
       </c>
-      <c r="AF6" s="2">
+      <c r="AG6" s="2">
         <v>28.9</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>14</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="5">
+        <v>1752801</v>
+      </c>
+      <c r="C7" t="s">
         <v>15</v>
       </c>
-      <c r="C7">
+      <c r="D7">
         <v>28</v>
       </c>
-      <c r="D7">
+      <c r="E7">
         <v>10</v>
       </c>
-      <c r="E7">
+      <c r="F7">
         <v>1</v>
       </c>
-      <c r="G7" s="2" t="s">
+      <c r="H7" s="2" t="s">
         <v>90</v>
-      </c>
-      <c r="H7" s="2">
-        <v>33</v>
       </c>
       <c r="I7" s="2">
         <v>33</v>
       </c>
       <c r="J7" s="2">
+        <v>33</v>
+      </c>
+      <c r="K7" s="2">
         <v>35.6</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>9.3000000000000007</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>19.899999999999999</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>0.46500000000000002</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>2.1</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>6.1</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>0.34</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>7.2</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>13.9</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>0.52</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>0.51700000000000002</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>6.1</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>7.3</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>0.83799999999999997</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>1.1000000000000001</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>5.0999999999999996</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>6.2</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>9.6999999999999993</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>1.5</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>0.8</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>4</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>3.4</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>26.7</v>
       </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>16</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="5">
+        <v>304316</v>
+      </c>
+      <c r="C8" t="s">
         <v>17</v>
       </c>
-      <c r="C8">
+      <c r="D8">
         <v>11</v>
       </c>
-      <c r="D8">
+      <c r="E8">
         <v>25</v>
       </c>
-      <c r="E8">
+      <c r="F8">
         <v>13</v>
       </c>
-      <c r="G8" s="2" t="s">
+      <c r="H8" s="2" t="s">
         <v>92</v>
-      </c>
-      <c r="H8" s="2">
-        <v>29</v>
       </c>
       <c r="I8" s="2">
         <v>29</v>
       </c>
       <c r="J8" s="2">
+        <v>29</v>
+      </c>
+      <c r="K8" s="2">
         <v>33.1</v>
       </c>
-      <c r="K8" s="2">
+      <c r="L8" s="2">
         <v>9.1999999999999993</v>
       </c>
-      <c r="L8" s="2">
+      <c r="M8" s="2">
         <v>18.7</v>
       </c>
-      <c r="M8" s="2">
+      <c r="N8" s="2">
         <v>0.49</v>
       </c>
-      <c r="N8" s="2">
+      <c r="O8" s="2">
         <v>3.7</v>
       </c>
-      <c r="O8" s="2">
+      <c r="P8" s="2">
         <v>9.4</v>
       </c>
-      <c r="P8" s="2">
+      <c r="Q8" s="2">
         <v>0.39700000000000002</v>
       </c>
-      <c r="Q8" s="2">
+      <c r="R8" s="2">
         <v>5.4</v>
       </c>
-      <c r="R8" s="2">
+      <c r="S8" s="2">
         <v>9.3000000000000007</v>
       </c>
-      <c r="S8" s="2">
+      <c r="T8" s="2">
         <v>0.58299999999999996</v>
       </c>
-      <c r="T8" s="2">
+      <c r="U8" s="2">
         <v>0.58899999999999997</v>
       </c>
-      <c r="U8" s="2">
+      <c r="V8" s="2">
         <v>3.8</v>
       </c>
-      <c r="V8" s="2">
+      <c r="W8" s="2">
         <v>4.5999999999999996</v>
       </c>
-      <c r="W8" s="2">
+      <c r="X8" s="2">
         <v>0.83299999999999996</v>
       </c>
-      <c r="X8" s="2">
+      <c r="Y8" s="2">
         <v>1.3</v>
       </c>
-      <c r="Y8" s="2">
+      <c r="Z8" s="2">
         <v>6.2</v>
       </c>
-      <c r="Z8" s="2">
+      <c r="AA8" s="2">
         <v>7.4</v>
       </c>
-      <c r="AA8" s="2">
+      <c r="AB8" s="2">
         <v>3.4</v>
       </c>
-      <c r="AB8" s="2">
+      <c r="AC8" s="2">
         <v>1.1000000000000001</v>
       </c>
-      <c r="AC8" s="2">
+      <c r="AD8" s="2">
         <v>0.2</v>
       </c>
-      <c r="AD8" s="2">
+      <c r="AE8" s="2">
         <v>2.4</v>
       </c>
-      <c r="AE8" s="2">
+      <c r="AF8" s="2">
         <v>2.1</v>
       </c>
-      <c r="AF8" s="2">
+      <c r="AG8" s="2">
         <v>25.9</v>
       </c>
     </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>18</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="5">
+        <v>1</v>
+      </c>
+      <c r="C9" t="s">
         <v>19</v>
       </c>
-      <c r="C9">
+      <c r="D9">
         <v>20</v>
       </c>
-      <c r="D9">
+      <c r="E9">
         <v>19</v>
       </c>
-      <c r="E9">
+      <c r="F9">
         <v>8</v>
       </c>
-      <c r="F9" t="s">
+      <c r="G9" t="s">
         <v>94</v>
       </c>
-      <c r="G9" s="2" t="s">
+      <c r="H9" s="2" t="s">
         <v>93</v>
-      </c>
-      <c r="H9" s="2">
-        <v>33</v>
       </c>
       <c r="I9" s="2">
         <v>33</v>
       </c>
       <c r="J9" s="2">
+        <v>33</v>
+      </c>
+      <c r="K9" s="2">
         <v>30.8</v>
       </c>
-      <c r="K9" s="2">
+      <c r="L9" s="2">
         <v>7.9</v>
       </c>
-      <c r="L9" s="2">
+      <c r="M9" s="2">
         <v>16.399999999999999</v>
       </c>
-      <c r="M9" s="2">
+      <c r="N9" s="2">
         <v>0.48199999999999998</v>
       </c>
-      <c r="N9" s="2">
+      <c r="O9" s="2">
         <v>3</v>
       </c>
-      <c r="O9" s="2">
+      <c r="P9" s="2">
         <v>7.3</v>
       </c>
-      <c r="P9" s="2">
+      <c r="Q9" s="2">
         <v>0.41499999999999998</v>
       </c>
-      <c r="Q9" s="2">
+      <c r="R9" s="2">
         <v>4.9000000000000004</v>
       </c>
-      <c r="R9" s="2">
+      <c r="S9" s="2">
         <v>9.1</v>
       </c>
-      <c r="S9" s="2">
+      <c r="T9" s="2">
         <v>0.53700000000000003</v>
       </c>
-      <c r="T9" s="2">
+      <c r="U9" s="2">
         <v>0.57499999999999996</v>
       </c>
-      <c r="U9" s="2">
+      <c r="V9" s="2">
         <v>4.9000000000000004</v>
       </c>
-      <c r="V9" s="2">
+      <c r="W9" s="2">
         <v>5.7</v>
       </c>
-      <c r="W9" s="2">
+      <c r="X9" s="2">
         <v>0.85699999999999998</v>
       </c>
-      <c r="X9" s="2">
+      <c r="Y9" s="2">
         <v>0.4</v>
       </c>
-      <c r="Y9" s="2">
+      <c r="Z9" s="2">
         <v>3.4</v>
       </c>
-      <c r="Z9" s="2">
+      <c r="AA9" s="2">
         <v>3.7</v>
       </c>
-      <c r="AA9" s="2">
+      <c r="AB9" s="2">
         <v>2.7</v>
       </c>
-      <c r="AB9" s="2">
+      <c r="AC9" s="2">
         <v>1.3</v>
       </c>
-      <c r="AC9" s="2">
+      <c r="AD9" s="2">
         <v>0.2</v>
       </c>
-      <c r="AD9" s="2">
+      <c r="AE9" s="2">
         <v>2</v>
       </c>
-      <c r="AE9" s="2">
+      <c r="AF9" s="2">
         <v>2.2000000000000002</v>
       </c>
-      <c r="AF9" s="2">
+      <c r="AG9" s="2">
         <v>23.8</v>
       </c>
     </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>20</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="5">
+        <v>1</v>
+      </c>
+      <c r="C10" t="s">
         <v>5</v>
       </c>
-      <c r="C10">
+      <c r="D10">
         <v>21</v>
       </c>
-      <c r="D10">
+      <c r="E10">
         <v>16</v>
       </c>
-      <c r="E10">
+      <c r="F10">
         <v>5</v>
       </c>
-      <c r="G10" s="2" t="s">
+      <c r="H10" s="2" t="s">
         <v>91</v>
-      </c>
-      <c r="H10" s="2">
-        <v>19</v>
       </c>
       <c r="I10" s="2">
         <v>19</v>
       </c>
       <c r="J10" s="2">
+        <v>19</v>
+      </c>
+      <c r="K10" s="2">
         <v>29.2</v>
       </c>
-      <c r="K10" s="2">
+      <c r="L10" s="2">
         <v>8</v>
       </c>
-      <c r="L10" s="2">
+      <c r="M10" s="2">
         <v>17.100000000000001</v>
       </c>
-      <c r="M10" s="2">
+      <c r="N10" s="2">
         <v>0.46899999999999997</v>
       </c>
-      <c r="N10" s="2">
+      <c r="O10" s="2">
         <v>0.9</v>
       </c>
-      <c r="O10" s="2">
+      <c r="P10" s="2">
         <v>4.0999999999999996</v>
       </c>
-      <c r="P10" s="2">
+      <c r="Q10" s="2">
         <v>0.23400000000000001</v>
       </c>
-      <c r="Q10" s="2">
+      <c r="R10" s="2">
         <v>7.1</v>
       </c>
-      <c r="R10" s="2">
+      <c r="S10" s="2">
         <v>13</v>
       </c>
-      <c r="S10" s="2">
+      <c r="T10" s="2">
         <v>0.54300000000000004</v>
       </c>
-      <c r="T10" s="2">
+      <c r="U10" s="2">
         <v>0.497</v>
       </c>
-      <c r="U10" s="2">
+      <c r="V10" s="2">
         <v>6.6</v>
       </c>
-      <c r="V10" s="2">
+      <c r="W10" s="2">
         <v>7.8</v>
       </c>
-      <c r="W10" s="2">
+      <c r="X10" s="2">
         <v>0.83899999999999997</v>
       </c>
-      <c r="X10" s="2">
+      <c r="Y10" s="2">
         <v>2</v>
       </c>
-      <c r="Y10" s="2">
+      <c r="Z10" s="2">
         <v>5.0999999999999996</v>
       </c>
-      <c r="Z10" s="2">
+      <c r="AA10" s="2">
         <v>7.1</v>
       </c>
-      <c r="AA10" s="2">
+      <c r="AB10" s="2">
         <v>3.3</v>
       </c>
-      <c r="AB10" s="2">
+      <c r="AC10" s="2">
         <v>0.6</v>
       </c>
-      <c r="AC10" s="2">
+      <c r="AD10" s="2">
         <v>1.3</v>
       </c>
-      <c r="AD10" s="2">
+      <c r="AE10" s="2">
         <v>2.8</v>
       </c>
-      <c r="AE10" s="2">
+      <c r="AF10" s="2">
         <v>2.4</v>
       </c>
-      <c r="AF10" s="2">
+      <c r="AG10" s="2">
         <v>23.5</v>
       </c>
     </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>21</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" s="5">
+        <v>525789</v>
+      </c>
+      <c r="C11" t="s">
         <v>22</v>
       </c>
-      <c r="C11">
+      <c r="D11">
         <v>20</v>
       </c>
-      <c r="D11">
+      <c r="E11">
         <v>21</v>
       </c>
-      <c r="E11">
+      <c r="F11">
         <v>9</v>
       </c>
-      <c r="G11" s="2" t="s">
+      <c r="H11" s="2" t="s">
         <v>92</v>
-      </c>
-      <c r="H11" s="2">
-        <v>37</v>
       </c>
       <c r="I11" s="2">
         <v>37</v>
       </c>
       <c r="J11" s="2">
+        <v>37</v>
+      </c>
+      <c r="K11" s="2">
         <v>35.4</v>
       </c>
-      <c r="K11" s="2">
+      <c r="L11" s="2">
         <v>8.8000000000000007</v>
       </c>
-      <c r="L11" s="2">
+      <c r="M11" s="2">
         <v>16.8</v>
       </c>
-      <c r="M11" s="2">
+      <c r="N11" s="2">
         <v>0.52600000000000002</v>
       </c>
-      <c r="N11" s="2">
+      <c r="O11" s="2">
         <v>1.6</v>
       </c>
-      <c r="O11" s="2">
+      <c r="P11" s="2">
         <v>4.5</v>
       </c>
-      <c r="P11" s="2">
+      <c r="Q11" s="2">
         <v>0.37</v>
       </c>
-      <c r="Q11" s="2">
+      <c r="R11" s="2">
         <v>7.2</v>
       </c>
-      <c r="R11" s="2">
+      <c r="S11" s="2">
         <v>12.4</v>
       </c>
-      <c r="S11" s="2">
+      <c r="T11" s="2">
         <v>0.58199999999999996</v>
       </c>
-      <c r="T11" s="2">
+      <c r="U11" s="2">
         <v>0.57499999999999996</v>
       </c>
-      <c r="U11" s="2">
+      <c r="V11" s="2">
         <v>4.4000000000000004</v>
       </c>
-      <c r="V11" s="2">
+      <c r="W11" s="2">
         <v>5.5</v>
       </c>
-      <c r="W11" s="2">
+      <c r="X11" s="2">
         <v>0.78900000000000003</v>
       </c>
-      <c r="X11" s="2">
+      <c r="Y11" s="2">
         <v>1.4</v>
       </c>
-      <c r="Y11" s="2">
+      <c r="Z11" s="2">
         <v>8.8000000000000007</v>
       </c>
-      <c r="Z11" s="2">
+      <c r="AA11" s="2">
         <v>10.3</v>
       </c>
-      <c r="AA11" s="2">
+      <c r="AB11" s="2">
         <v>8.1999999999999993</v>
       </c>
-      <c r="AB11" s="2">
+      <c r="AC11" s="2">
         <v>1.3</v>
       </c>
-      <c r="AC11" s="2">
+      <c r="AD11" s="2">
         <v>0.5</v>
       </c>
-      <c r="AD11" s="2">
+      <c r="AE11" s="2">
         <v>3.5</v>
       </c>
-      <c r="AE11" s="2">
+      <c r="AF11" s="2">
         <v>2</v>
       </c>
-      <c r="AF11" s="2">
+      <c r="AG11" s="2">
         <v>23.7</v>
       </c>
     </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>23</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" s="5">
+        <v>298761</v>
+      </c>
+      <c r="C12" t="s">
         <v>24</v>
       </c>
-      <c r="C12">
+      <c r="D12">
         <v>8</v>
       </c>
-      <c r="D12">
+      <c r="E12">
         <v>31</v>
       </c>
-      <c r="E12">
+      <c r="F12">
         <v>15</v>
       </c>
-      <c r="G12" s="2" t="s">
+      <c r="H12" s="2" t="s">
         <v>86</v>
-      </c>
-      <c r="H12" s="2">
-        <v>38</v>
       </c>
       <c r="I12" s="2">
         <v>38</v>
       </c>
       <c r="J12" s="2">
+        <v>38</v>
+      </c>
+      <c r="K12" s="2">
         <v>33.799999999999997</v>
       </c>
-      <c r="K12" s="2">
+      <c r="L12" s="2">
         <v>8.6999999999999993</v>
       </c>
-      <c r="L12" s="2">
+      <c r="M12" s="2">
         <v>18.2</v>
       </c>
-      <c r="M12" s="2">
+      <c r="N12" s="2">
         <v>0.48</v>
       </c>
-      <c r="N12" s="2">
+      <c r="O12" s="2">
         <v>1.7</v>
       </c>
-      <c r="O12" s="2">
+      <c r="P12" s="2">
         <v>4.5</v>
       </c>
-      <c r="P12" s="2">
+      <c r="Q12" s="2">
         <v>0.372</v>
       </c>
-      <c r="Q12" s="2">
+      <c r="R12" s="2">
         <v>7.1</v>
       </c>
-      <c r="R12" s="2">
+      <c r="S12" s="2">
         <v>13.7</v>
       </c>
-      <c r="S12" s="2">
+      <c r="T12" s="2">
         <v>0.51500000000000001</v>
       </c>
-      <c r="T12" s="2">
+      <c r="U12" s="2">
         <v>0.52600000000000002</v>
       </c>
-      <c r="U12" s="2">
+      <c r="V12" s="2">
         <v>4.4000000000000004</v>
       </c>
-      <c r="V12" s="2">
+      <c r="W12" s="2">
         <v>6.4</v>
       </c>
-      <c r="W12" s="2">
+      <c r="X12" s="2">
         <v>0.68700000000000006</v>
       </c>
-      <c r="X12" s="2">
+      <c r="Y12" s="2">
         <v>1.7</v>
       </c>
-      <c r="Y12" s="2">
+      <c r="Z12" s="2">
         <v>5.2</v>
       </c>
-      <c r="Z12" s="2">
+      <c r="AA12" s="2">
         <v>6.8</v>
       </c>
-      <c r="AA12" s="2">
+      <c r="AB12" s="2">
         <v>3.8</v>
       </c>
-      <c r="AB12" s="2">
+      <c r="AC12" s="2">
         <v>1.3</v>
       </c>
-      <c r="AC12" s="2">
+      <c r="AD12" s="2">
         <v>0.4</v>
       </c>
-      <c r="AD12" s="2">
+      <c r="AE12" s="2">
         <v>2.2000000000000002</v>
       </c>
-      <c r="AE12" s="2">
+      <c r="AF12" s="2">
         <v>2.6</v>
       </c>
-      <c r="AF12" s="2">
+      <c r="AG12" s="2">
         <v>23.6</v>
       </c>
-      <c r="AG12" s="2"/>
+      <c r="AH12" s="2"/>
     </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>25</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" s="5">
+        <v>1</v>
+      </c>
+      <c r="C13" t="s">
         <v>26</v>
       </c>
-      <c r="C13">
+      <c r="D13">
         <v>22</v>
       </c>
-      <c r="D13">
+      <c r="E13">
         <v>18</v>
       </c>
-      <c r="E13">
+      <c r="F13">
         <v>6</v>
       </c>
-      <c r="G13" s="2" t="s">
+      <c r="H13" s="2" t="s">
         <v>92</v>
-      </c>
-      <c r="H13" s="2">
-        <v>24</v>
       </c>
       <c r="I13" s="2">
         <v>24</v>
       </c>
       <c r="J13" s="2">
+        <v>24</v>
+      </c>
+      <c r="K13" s="2">
         <v>33.4</v>
       </c>
-      <c r="K13" s="2">
+      <c r="L13" s="2">
         <v>7.8</v>
       </c>
-      <c r="L13" s="2">
+      <c r="M13" s="2">
         <v>15.9</v>
       </c>
-      <c r="M13" s="2">
+      <c r="N13" s="2">
         <v>0.49</v>
       </c>
-      <c r="N13" s="2">
+      <c r="O13" s="2">
         <v>1.5</v>
       </c>
-      <c r="O13" s="2">
+      <c r="P13" s="2">
         <v>4.2</v>
       </c>
-      <c r="P13" s="2">
+      <c r="Q13" s="2">
         <v>0.36</v>
       </c>
-      <c r="Q13" s="2">
+      <c r="R13" s="2">
         <v>6.3</v>
       </c>
-      <c r="R13" s="2">
+      <c r="S13" s="2">
         <v>11.8</v>
       </c>
-      <c r="S13" s="2">
+      <c r="T13" s="2">
         <v>0.53500000000000003</v>
       </c>
-      <c r="T13" s="2">
+      <c r="U13" s="2">
         <v>0.53700000000000003</v>
       </c>
-      <c r="U13" s="2">
+      <c r="V13" s="2">
         <v>5.6</v>
       </c>
-      <c r="V13" s="2">
+      <c r="W13" s="2">
         <v>6.8</v>
       </c>
-      <c r="W13" s="2">
+      <c r="X13" s="2">
         <v>0.82299999999999995</v>
       </c>
-      <c r="X13" s="2">
+      <c r="Y13" s="2">
         <v>1.5</v>
       </c>
-      <c r="Y13" s="2">
+      <c r="Z13" s="2">
         <v>4.5999999999999996</v>
       </c>
-      <c r="Z13" s="2">
+      <c r="AA13" s="2">
         <v>6.1</v>
       </c>
-      <c r="AA13" s="2">
+      <c r="AB13" s="2">
         <v>3.7</v>
       </c>
-      <c r="AB13" s="2">
+      <c r="AC13" s="2">
         <v>1.2</v>
       </c>
-      <c r="AC13" s="2">
+      <c r="AD13" s="2">
         <v>0.4</v>
       </c>
-      <c r="AD13" s="2">
+      <c r="AE13" s="2">
         <v>1.8</v>
       </c>
-      <c r="AE13" s="2">
+      <c r="AF13" s="2">
         <v>2.2000000000000002</v>
       </c>
-      <c r="AF13" s="2">
+      <c r="AG13" s="2">
         <v>22.7</v>
       </c>
     </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>27</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" s="5">
+        <v>1</v>
+      </c>
+      <c r="C14" t="s">
         <v>19</v>
       </c>
-      <c r="C14">
+      <c r="D14">
         <v>20</v>
       </c>
-      <c r="D14">
+      <c r="E14">
         <v>19</v>
       </c>
-      <c r="E14">
+      <c r="F14">
         <v>8</v>
       </c>
-      <c r="F14" t="s">
+      <c r="G14" t="s">
         <v>94</v>
       </c>
-      <c r="G14" s="2" t="s">
+      <c r="H14" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="H14" s="2">
+      <c r="I14" s="2">
         <v>9</v>
       </c>
-      <c r="I14" s="2">
+      <c r="J14" s="2">
         <v>8</v>
       </c>
-      <c r="J14" s="2">
+      <c r="K14" s="2">
         <v>31</v>
       </c>
-      <c r="K14" s="2">
+      <c r="L14" s="2">
         <v>8.1</v>
       </c>
-      <c r="L14" s="2">
+      <c r="M14" s="2">
         <v>16.399999999999999</v>
       </c>
-      <c r="M14" s="2">
+      <c r="N14" s="2">
         <v>0.49299999999999999</v>
       </c>
-      <c r="N14" s="2">
+      <c r="O14" s="2">
         <v>2</v>
       </c>
-      <c r="O14" s="2">
+      <c r="P14" s="2">
         <v>5.8</v>
       </c>
-      <c r="P14" s="2">
+      <c r="Q14" s="2">
         <v>0.34599999999999997</v>
       </c>
-      <c r="Q14" s="2">
+      <c r="R14" s="2">
         <v>6.1</v>
       </c>
-      <c r="R14" s="2">
+      <c r="S14" s="2">
         <v>10.7</v>
       </c>
-      <c r="S14" s="2">
+      <c r="T14" s="2">
         <v>0.57299999999999995</v>
       </c>
-      <c r="T14" s="2">
+      <c r="U14" s="2">
         <v>0.55400000000000005</v>
       </c>
-      <c r="U14" s="2">
+      <c r="V14" s="2">
         <v>3.6</v>
       </c>
-      <c r="V14" s="2">
+      <c r="W14" s="2">
         <v>3.9</v>
       </c>
-      <c r="W14" s="2">
+      <c r="X14" s="2">
         <v>0.91400000000000003</v>
       </c>
-      <c r="X14" s="2">
+      <c r="Y14" s="2">
         <v>0.4</v>
       </c>
-      <c r="Y14" s="2">
+      <c r="Z14" s="2">
         <v>4.9000000000000004</v>
       </c>
-      <c r="Z14" s="2">
+      <c r="AA14" s="2">
         <v>5.3</v>
       </c>
-      <c r="AA14" s="2">
+      <c r="AB14" s="2">
         <v>2.7</v>
       </c>
-      <c r="AB14" s="2">
+      <c r="AC14" s="2">
         <v>0.8</v>
       </c>
-      <c r="AC14" s="2">
+      <c r="AD14" s="2">
         <v>0.4</v>
       </c>
-      <c r="AD14" s="2">
+      <c r="AE14" s="2">
         <v>1.3</v>
       </c>
-      <c r="AE14" s="2">
+      <c r="AF14" s="2">
         <v>2</v>
       </c>
-      <c r="AF14" s="2">
+      <c r="AG14" s="2">
         <v>21.8</v>
       </c>
-      <c r="AG14" s="2"/>
+      <c r="AH14" s="2"/>
     </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>28</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" s="5">
+        <v>281799</v>
+      </c>
+      <c r="C15" t="s">
         <v>29</v>
       </c>
-      <c r="C15">
+      <c r="D15">
         <v>24</v>
       </c>
-      <c r="D15">
+      <c r="E15">
         <v>16</v>
       </c>
-      <c r="E15">
+      <c r="F15">
         <v>4</v>
       </c>
-      <c r="F15" t="s">
+      <c r="G15" t="s">
         <v>94</v>
       </c>
-      <c r="G15" s="2" t="s">
+      <c r="H15" s="2" t="s">
         <v>92</v>
-      </c>
-      <c r="H15" s="2">
-        <v>38</v>
       </c>
       <c r="I15" s="2">
         <v>38</v>
       </c>
       <c r="J15" s="2">
+        <v>38</v>
+      </c>
+      <c r="K15" s="2">
         <v>33.700000000000003</v>
       </c>
-      <c r="K15" s="2">
+      <c r="L15" s="2">
         <v>8.1999999999999993</v>
       </c>
-      <c r="L15" s="2">
+      <c r="M15" s="2">
         <v>17.2</v>
       </c>
-      <c r="M15" s="2">
+      <c r="N15" s="2">
         <v>0.47399999999999998</v>
       </c>
-      <c r="N15" s="2">
+      <c r="O15" s="2">
         <v>1.7</v>
       </c>
-      <c r="O15" s="2">
+      <c r="P15" s="2">
         <v>5</v>
       </c>
-      <c r="P15" s="2">
+      <c r="Q15" s="2">
         <v>0.34899999999999998</v>
       </c>
-      <c r="Q15" s="2">
+      <c r="R15" s="2">
         <v>6.4</v>
       </c>
-      <c r="R15" s="2">
+      <c r="S15" s="2">
         <v>12.2</v>
       </c>
-      <c r="S15" s="2">
+      <c r="T15" s="2">
         <v>0.52500000000000002</v>
       </c>
-      <c r="T15" s="2">
+      <c r="U15" s="2">
         <v>0.52400000000000002</v>
       </c>
-      <c r="U15" s="2">
+      <c r="V15" s="2">
         <v>3.7</v>
       </c>
-      <c r="V15" s="2">
+      <c r="W15" s="2">
         <v>4.5999999999999996</v>
       </c>
-      <c r="W15" s="2">
+      <c r="X15" s="2">
         <v>0.82099999999999995</v>
       </c>
-      <c r="X15" s="2">
+      <c r="Y15" s="2">
         <v>0.8</v>
       </c>
-      <c r="Y15" s="2">
+      <c r="Z15" s="2">
         <v>5.0999999999999996</v>
       </c>
-      <c r="Z15" s="2">
+      <c r="AA15" s="2">
         <v>5.9</v>
       </c>
-      <c r="AA15" s="2">
+      <c r="AB15" s="2">
         <v>3.6</v>
-      </c>
-      <c r="AB15" s="2">
-        <v>0.8</v>
       </c>
       <c r="AC15" s="2">
         <v>0.8</v>
       </c>
       <c r="AD15" s="2">
+        <v>0.8</v>
+      </c>
+      <c r="AE15" s="2">
         <v>2.8</v>
       </c>
-      <c r="AE15" s="2">
+      <c r="AF15" s="2">
         <v>1.9</v>
       </c>
-      <c r="AF15" s="2">
+      <c r="AG15" s="2">
         <v>21.8</v>
       </c>
     </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>30</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16" s="5">
+        <v>898038</v>
+      </c>
+      <c r="C16" t="s">
         <v>13</v>
       </c>
-      <c r="C16">
+      <c r="D16">
         <v>25</v>
       </c>
-      <c r="D16">
+      <c r="E16">
         <v>14</v>
       </c>
-      <c r="E16">
+      <c r="F16">
         <v>2</v>
       </c>
-      <c r="G16" s="2" t="s">
+      <c r="H16" s="2" t="s">
         <v>91</v>
-      </c>
-      <c r="H16" s="2">
-        <v>36</v>
       </c>
       <c r="I16" s="2">
         <v>36</v>
       </c>
       <c r="J16" s="2">
+        <v>36</v>
+      </c>
+      <c r="K16" s="2">
         <v>32.299999999999997</v>
       </c>
-      <c r="K16" s="2">
+      <c r="L16" s="2">
         <v>6.8</v>
       </c>
-      <c r="L16" s="2">
+      <c r="M16" s="2">
         <v>14.5</v>
       </c>
-      <c r="M16" s="2">
+      <c r="N16" s="2">
         <v>0.47099999999999997</v>
       </c>
-      <c r="N16" s="2">
+      <c r="O16" s="2">
         <v>1.7</v>
       </c>
-      <c r="O16" s="2">
+      <c r="P16" s="2">
         <v>4.8</v>
       </c>
-      <c r="P16" s="2">
+      <c r="Q16" s="2">
         <v>0.35499999999999998</v>
       </c>
-      <c r="Q16" s="2">
+      <c r="R16" s="2">
         <v>5.0999999999999996</v>
       </c>
-      <c r="R16" s="2">
+      <c r="S16" s="2">
         <v>9.6999999999999993</v>
       </c>
-      <c r="S16" s="2">
+      <c r="T16" s="2">
         <v>0.52900000000000003</v>
       </c>
-      <c r="T16" s="2">
+      <c r="U16" s="2">
         <v>0.53</v>
       </c>
-      <c r="U16" s="2">
+      <c r="V16" s="2">
         <v>5.9</v>
       </c>
-      <c r="V16" s="2">
+      <c r="W16" s="2">
         <v>6.8</v>
       </c>
-      <c r="W16" s="2">
+      <c r="X16" s="2">
         <v>0.86499999999999999</v>
       </c>
-      <c r="X16" s="2">
+      <c r="Y16" s="2">
         <v>2.9</v>
       </c>
-      <c r="Y16" s="2">
+      <c r="Z16" s="2">
         <v>8.5</v>
       </c>
-      <c r="Z16" s="2">
+      <c r="AA16" s="2">
         <v>11.4</v>
       </c>
-      <c r="AA16" s="2">
+      <c r="AB16" s="2">
         <v>3</v>
       </c>
-      <c r="AB16" s="2">
+      <c r="AC16" s="2">
         <v>0.8</v>
       </c>
-      <c r="AC16" s="2">
+      <c r="AD16" s="2">
         <v>0.7</v>
       </c>
-      <c r="AD16" s="2">
+      <c r="AE16" s="2">
         <v>2.6</v>
       </c>
-      <c r="AE16" s="2">
+      <c r="AF16" s="2">
         <v>3.5</v>
       </c>
-      <c r="AF16" s="2">
+      <c r="AG16" s="2">
         <v>21.2</v>
       </c>
     </row>
-    <row r="17" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>31</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B17" s="5">
+        <v>1</v>
+      </c>
+      <c r="C17" t="s">
         <v>26</v>
       </c>
-      <c r="C17">
+      <c r="D17">
         <v>22</v>
       </c>
-      <c r="D17">
+      <c r="E17">
         <v>18</v>
       </c>
-      <c r="E17">
+      <c r="F17">
         <v>6</v>
       </c>
-      <c r="F17" t="s">
+      <c r="G17" t="s">
         <v>94</v>
       </c>
-      <c r="G17" s="2" t="s">
+      <c r="H17" s="2" t="s">
         <v>86</v>
-      </c>
-      <c r="H17" s="2">
-        <v>30</v>
       </c>
       <c r="I17" s="2">
         <v>30</v>
       </c>
       <c r="J17" s="2">
+        <v>30</v>
+      </c>
+      <c r="K17" s="2">
         <v>33.700000000000003</v>
       </c>
-      <c r="K17" s="2">
+      <c r="L17" s="2">
         <v>7.1</v>
       </c>
-      <c r="L17" s="2">
+      <c r="M17" s="2">
         <v>15.6</v>
       </c>
-      <c r="M17" s="2">
+      <c r="N17" s="2">
         <v>0.45300000000000001</v>
       </c>
-      <c r="N17" s="2">
+      <c r="O17" s="2">
         <v>0.9</v>
       </c>
-      <c r="O17" s="2">
+      <c r="P17" s="2">
         <v>3.6</v>
       </c>
-      <c r="P17" s="2">
+      <c r="Q17" s="2">
         <v>0.252</v>
       </c>
-      <c r="Q17" s="2">
+      <c r="R17" s="2">
         <v>6.2</v>
       </c>
-      <c r="R17" s="2">
+      <c r="S17" s="2">
         <v>12</v>
       </c>
-      <c r="S17" s="2">
+      <c r="T17" s="2">
         <v>0.51200000000000001</v>
       </c>
-      <c r="T17" s="2">
+      <c r="U17" s="2">
         <v>0.48199999999999998</v>
       </c>
-      <c r="U17" s="2">
+      <c r="V17" s="2">
         <v>5.9</v>
       </c>
-      <c r="V17" s="2">
+      <c r="W17" s="2">
         <v>7.8</v>
       </c>
-      <c r="W17" s="2">
+      <c r="X17" s="2">
         <v>0.755</v>
       </c>
-      <c r="X17" s="2">
+      <c r="Y17" s="2">
         <v>0.9</v>
       </c>
-      <c r="Y17" s="2">
+      <c r="Z17" s="2">
         <v>7.7</v>
       </c>
-      <c r="Z17" s="2">
+      <c r="AA17" s="2">
         <v>8.6999999999999993</v>
       </c>
-      <c r="AA17" s="2">
+      <c r="AB17" s="2">
         <v>4.9000000000000004</v>
       </c>
-      <c r="AB17" s="2">
+      <c r="AC17" s="2">
         <v>0.6</v>
       </c>
-      <c r="AC17" s="2">
+      <c r="AD17" s="2">
         <v>0.7</v>
       </c>
-      <c r="AD17" s="2">
+      <c r="AE17" s="2">
         <v>2.9</v>
       </c>
-      <c r="AE17" s="2">
+      <c r="AF17" s="2">
         <v>2.2000000000000002</v>
       </c>
-      <c r="AF17" s="2">
+      <c r="AG17" s="2">
         <v>20.9</v>
       </c>
     </row>
-    <row r="18" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>32</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B18" s="5">
+        <v>1</v>
+      </c>
+      <c r="C18" t="s">
         <v>22</v>
       </c>
-      <c r="C18">
+      <c r="D18">
         <v>20</v>
       </c>
-      <c r="D18">
+      <c r="E18">
         <v>21</v>
       </c>
-      <c r="E18">
+      <c r="F18">
         <v>9</v>
       </c>
-      <c r="F18" t="s">
+      <c r="G18" t="s">
         <v>95</v>
       </c>
-      <c r="G18" s="2" t="s">
+      <c r="H18" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="H18" s="2">
+      <c r="I18" s="2">
         <v>39</v>
       </c>
-      <c r="I18" s="2">
+      <c r="J18" s="2">
         <v>32</v>
       </c>
-      <c r="J18" s="2">
+      <c r="K18" s="2">
         <v>32.9</v>
       </c>
-      <c r="K18" s="2">
+      <c r="L18" s="2">
         <v>7.1</v>
       </c>
-      <c r="L18" s="2">
+      <c r="M18" s="2">
         <v>16</v>
       </c>
-      <c r="M18" s="2">
+      <c r="N18" s="2">
         <v>0.44500000000000001</v>
       </c>
-      <c r="N18" s="2">
+      <c r="O18" s="2">
         <v>3</v>
       </c>
-      <c r="O18" s="2">
+      <c r="P18" s="2">
         <v>8</v>
       </c>
-      <c r="P18" s="2">
+      <c r="Q18" s="2">
         <v>0.372</v>
       </c>
-      <c r="Q18" s="2">
+      <c r="R18" s="2">
         <v>4.2</v>
       </c>
-      <c r="R18" s="2">
+      <c r="S18" s="2">
         <v>8</v>
       </c>
-      <c r="S18" s="2">
+      <c r="T18" s="2">
         <v>0.51800000000000002</v>
       </c>
-      <c r="T18" s="2">
+      <c r="U18" s="2">
         <v>0.53800000000000003</v>
       </c>
-      <c r="U18" s="2">
+      <c r="V18" s="2">
         <v>3.3</v>
       </c>
-      <c r="V18" s="2">
+      <c r="W18" s="2">
         <v>3.9</v>
       </c>
-      <c r="W18" s="2">
+      <c r="X18" s="2">
         <v>0.86099999999999999</v>
       </c>
-      <c r="X18" s="2">
+      <c r="Y18" s="2">
         <v>0.6</v>
       </c>
-      <c r="Y18" s="2">
+      <c r="Z18" s="2">
         <v>2.9</v>
       </c>
-      <c r="Z18" s="2">
+      <c r="AA18" s="2">
         <v>3.6</v>
       </c>
-      <c r="AA18" s="2">
+      <c r="AB18" s="2">
         <v>3.3</v>
       </c>
-      <c r="AB18" s="2">
+      <c r="AC18" s="2">
         <v>1.1000000000000001</v>
       </c>
-      <c r="AC18" s="2">
+      <c r="AD18" s="2">
         <v>0.6</v>
-      </c>
-      <c r="AD18" s="2">
-        <v>2.1</v>
       </c>
       <c r="AE18" s="2">
         <v>2.1</v>
       </c>
       <c r="AF18" s="2">
+        <v>2.1</v>
+      </c>
+      <c r="AG18" s="2">
         <v>20.6</v>
       </c>
     </row>
-    <row r="19" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>33</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B19" s="5">
+        <v>261883</v>
+      </c>
+      <c r="C19" t="s">
         <v>34</v>
       </c>
-      <c r="C19">
+      <c r="D19">
         <v>14</v>
       </c>
-      <c r="D19">
+      <c r="E19">
         <v>25</v>
       </c>
-      <c r="E19">
+      <c r="F19">
         <v>12</v>
       </c>
-      <c r="G19" s="2" t="s">
+      <c r="H19" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="H19" s="2">
+      <c r="I19" s="2">
         <v>29</v>
       </c>
-      <c r="I19" s="2">
+      <c r="J19" s="2">
         <v>28</v>
       </c>
-      <c r="J19" s="2">
+      <c r="K19" s="2">
         <v>27.8</v>
       </c>
-      <c r="K19" s="2">
+      <c r="L19" s="2">
         <v>6.9</v>
       </c>
-      <c r="L19" s="2">
+      <c r="M19" s="2">
         <v>16.7</v>
       </c>
-      <c r="M19" s="2">
+      <c r="N19" s="2">
         <v>0.41299999999999998</v>
       </c>
-      <c r="N19" s="2">
+      <c r="O19" s="2">
         <v>3.4</v>
       </c>
-      <c r="O19" s="2">
+      <c r="P19" s="2">
         <v>9</v>
       </c>
-      <c r="P19" s="2">
+      <c r="Q19" s="2">
         <v>0.374</v>
       </c>
-      <c r="Q19" s="2">
+      <c r="R19" s="2">
         <v>3.5</v>
       </c>
-      <c r="R19" s="2">
+      <c r="S19" s="2">
         <v>7.7</v>
       </c>
-      <c r="S19" s="2">
+      <c r="T19" s="2">
         <v>0.45900000000000002</v>
       </c>
-      <c r="T19" s="2">
+      <c r="U19" s="2">
         <v>0.51400000000000001</v>
       </c>
-      <c r="U19" s="2">
+      <c r="V19" s="2">
         <v>2.7</v>
       </c>
-      <c r="V19" s="2">
+      <c r="W19" s="2">
         <v>3.1</v>
       </c>
-      <c r="W19" s="2">
+      <c r="X19" s="2">
         <v>0.878</v>
       </c>
-      <c r="X19" s="2">
+      <c r="Y19" s="2">
         <v>0.9</v>
       </c>
-      <c r="Y19" s="2">
+      <c r="Z19" s="2">
         <v>4.0999999999999996</v>
       </c>
-      <c r="Z19" s="2">
+      <c r="AA19" s="2">
         <v>5</v>
       </c>
-      <c r="AA19" s="2">
+      <c r="AB19" s="2">
         <v>7.8</v>
       </c>
-      <c r="AB19" s="2">
+      <c r="AC19" s="2">
         <v>1.2</v>
       </c>
-      <c r="AC19" s="2">
+      <c r="AD19" s="2">
         <v>0.2</v>
       </c>
-      <c r="AD19" s="2">
+      <c r="AE19" s="2">
         <v>3.4</v>
       </c>
-      <c r="AE19" s="2">
+      <c r="AF19" s="2">
         <v>2.8</v>
       </c>
-      <c r="AF19" s="2">
+      <c r="AG19" s="2">
         <v>19.899999999999999</v>
       </c>
-      <c r="AG19" s="2"/>
+      <c r="AH19" s="2"/>
     </row>
-    <row r="20" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>35</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B20" s="5">
+        <v>1</v>
+      </c>
+      <c r="C20" t="s">
         <v>34</v>
       </c>
-      <c r="C20">
+      <c r="D20">
         <v>14</v>
       </c>
-      <c r="D20">
+      <c r="E20">
         <v>25</v>
       </c>
-      <c r="E20">
+      <c r="F20">
         <v>12</v>
       </c>
-      <c r="G20" s="2" t="s">
+      <c r="H20" s="2" t="s">
         <v>86</v>
-      </c>
-      <c r="H20" s="2">
-        <v>38</v>
       </c>
       <c r="I20" s="2">
         <v>38</v>
       </c>
       <c r="J20" s="2">
+        <v>38</v>
+      </c>
+      <c r="K20" s="2">
         <v>33.4</v>
       </c>
-      <c r="K20" s="2">
+      <c r="L20" s="2">
         <v>6.9</v>
       </c>
-      <c r="L20" s="2">
+      <c r="M20" s="2">
         <v>15.6</v>
       </c>
-      <c r="M20" s="2">
+      <c r="N20" s="2">
         <v>0.44500000000000001</v>
       </c>
-      <c r="N20" s="2">
+      <c r="O20" s="2">
         <v>2.2999999999999998</v>
       </c>
-      <c r="O20" s="2">
+      <c r="P20" s="2">
         <v>7</v>
       </c>
-      <c r="P20" s="2">
+      <c r="Q20" s="2">
         <v>0.33500000000000002</v>
       </c>
-      <c r="Q20" s="2">
+      <c r="R20" s="2">
         <v>4.5999999999999996</v>
       </c>
-      <c r="R20" s="2">
+      <c r="S20" s="2">
         <v>8.6</v>
       </c>
-      <c r="S20" s="2">
+      <c r="T20" s="2">
         <v>0.53500000000000003</v>
       </c>
-      <c r="T20" s="2">
+      <c r="U20" s="2">
         <v>0.52</v>
       </c>
-      <c r="U20" s="2">
+      <c r="V20" s="2">
         <v>3.5</v>
       </c>
-      <c r="V20" s="2">
+      <c r="W20" s="2">
         <v>4.2</v>
       </c>
-      <c r="W20" s="2">
+      <c r="X20" s="2">
         <v>0.84199999999999997</v>
       </c>
-      <c r="X20" s="2">
+      <c r="Y20" s="2">
         <v>0.9</v>
       </c>
-      <c r="Y20" s="2">
+      <c r="Z20" s="2">
         <v>5.6</v>
       </c>
-      <c r="Z20" s="2">
+      <c r="AA20" s="2">
         <v>6.4</v>
       </c>
-      <c r="AA20" s="2">
+      <c r="AB20" s="2">
         <v>3.7</v>
-      </c>
-      <c r="AB20" s="2">
-        <v>0.6</v>
       </c>
       <c r="AC20" s="2">
         <v>0.6</v>
       </c>
       <c r="AD20" s="2">
+        <v>0.6</v>
+      </c>
+      <c r="AE20" s="2">
         <v>1.5</v>
       </c>
-      <c r="AE20" s="2">
+      <c r="AF20" s="2">
         <v>1.8</v>
       </c>
-      <c r="AF20" s="2">
+      <c r="AG20" s="2">
         <v>19.7</v>
       </c>
     </row>
-    <row r="21" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>36</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B21" s="5">
+        <v>1</v>
+      </c>
+      <c r="C21" t="s">
         <v>29</v>
       </c>
-      <c r="C21">
+      <c r="D21">
         <v>24</v>
       </c>
-      <c r="D21">
+      <c r="E21">
         <v>16</v>
       </c>
-      <c r="E21">
+      <c r="F21">
         <v>4</v>
       </c>
-      <c r="F21" t="s">
+      <c r="G21" t="s">
         <v>95</v>
       </c>
-      <c r="G21" s="2" t="s">
+      <c r="H21" s="2" t="s">
         <v>92</v>
-      </c>
-      <c r="H21" s="2">
-        <v>23</v>
       </c>
       <c r="I21" s="2">
         <v>23</v>
       </c>
       <c r="J21" s="2">
+        <v>23</v>
+      </c>
+      <c r="K21" s="2">
         <v>30.3</v>
       </c>
-      <c r="K21" s="2">
+      <c r="L21" s="2">
         <v>7.3</v>
       </c>
-      <c r="L21" s="2">
+      <c r="M21" s="2">
         <v>14.7</v>
       </c>
-      <c r="M21" s="2">
+      <c r="N21" s="2">
         <v>0.496</v>
       </c>
-      <c r="N21" s="2">
+      <c r="O21" s="2">
         <v>1.9</v>
       </c>
-      <c r="O21" s="2">
+      <c r="P21" s="2">
         <v>5.4</v>
       </c>
-      <c r="P21" s="2">
+      <c r="Q21" s="2">
         <v>0.35499999999999998</v>
       </c>
-      <c r="Q21" s="2">
+      <c r="R21" s="2">
         <v>5.4</v>
       </c>
-      <c r="R21" s="2">
+      <c r="S21" s="2">
         <v>9.3000000000000007</v>
       </c>
-      <c r="S21" s="2">
+      <c r="T21" s="2">
         <v>0.57699999999999996</v>
       </c>
-      <c r="T21" s="2">
+      <c r="U21" s="2">
         <v>0.56000000000000005</v>
       </c>
-      <c r="U21" s="2">
+      <c r="V21" s="2">
         <v>3.1</v>
       </c>
-      <c r="V21" s="2">
+      <c r="W21" s="2">
         <v>4.5</v>
       </c>
-      <c r="W21" s="2">
+      <c r="X21" s="2">
         <v>0.68899999999999995</v>
       </c>
-      <c r="X21" s="2">
+      <c r="Y21" s="2">
         <v>0.8</v>
       </c>
-      <c r="Y21" s="2">
+      <c r="Z21" s="2">
         <v>4.3</v>
       </c>
-      <c r="Z21" s="2">
+      <c r="AA21" s="2">
         <v>5</v>
       </c>
-      <c r="AA21" s="2">
+      <c r="AB21" s="2">
         <v>3.7</v>
       </c>
-      <c r="AB21" s="2">
+      <c r="AC21" s="2">
         <v>0.8</v>
       </c>
-      <c r="AC21" s="2">
+      <c r="AD21" s="2">
         <v>0.2</v>
       </c>
-      <c r="AD21" s="2">
+      <c r="AE21" s="2">
         <v>1.6</v>
       </c>
-      <c r="AE21" s="2">
+      <c r="AF21" s="2">
         <v>2.4</v>
       </c>
-      <c r="AF21" s="2">
+      <c r="AG21" s="2">
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="22" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>37</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B22" s="5">
+        <v>1</v>
+      </c>
+      <c r="C22" t="s">
         <v>34</v>
       </c>
-      <c r="C22">
+      <c r="D22">
         <v>14</v>
       </c>
-      <c r="D22">
+      <c r="E22">
         <v>25</v>
       </c>
-      <c r="E22">
+      <c r="F22">
         <v>12</v>
       </c>
-      <c r="G22" s="2" t="s">
+      <c r="H22" s="2" t="s">
         <v>92</v>
-      </c>
-      <c r="H22" s="2">
-        <v>22</v>
       </c>
       <c r="I22" s="2">
         <v>22</v>
       </c>
       <c r="J22" s="2">
+        <v>22</v>
+      </c>
+      <c r="K22" s="2">
         <v>29.7</v>
       </c>
-      <c r="K22" s="2">
+      <c r="L22" s="2">
         <v>6.7</v>
       </c>
-      <c r="L22" s="2">
+      <c r="M22" s="2">
         <v>16.8</v>
       </c>
-      <c r="M22" s="2">
+      <c r="N22" s="2">
         <v>0.4</v>
       </c>
-      <c r="N22" s="2">
+      <c r="O22" s="2">
         <v>2.8</v>
       </c>
-      <c r="O22" s="2">
+      <c r="P22" s="2">
         <v>8.1</v>
       </c>
-      <c r="P22" s="2">
+      <c r="Q22" s="2">
         <v>0.34799999999999998</v>
       </c>
-      <c r="Q22" s="2">
+      <c r="R22" s="2">
         <v>3.9</v>
       </c>
-      <c r="R22" s="2">
+      <c r="S22" s="2">
         <v>8.6999999999999993</v>
       </c>
-      <c r="S22" s="2">
+      <c r="T22" s="2">
         <v>0.44800000000000001</v>
       </c>
-      <c r="T22" s="2">
+      <c r="U22" s="2">
         <v>0.48399999999999999</v>
       </c>
-      <c r="U22" s="2">
+      <c r="V22" s="2">
         <v>3.1</v>
       </c>
-      <c r="V22" s="2">
+      <c r="W22" s="2">
         <v>3.7</v>
       </c>
-      <c r="W22" s="2">
+      <c r="X22" s="2">
         <v>0.84</v>
       </c>
-      <c r="X22" s="2">
+      <c r="Y22" s="2">
         <v>1.1000000000000001</v>
       </c>
-      <c r="Y22" s="2">
+      <c r="Z22" s="2">
         <v>3.1</v>
       </c>
-      <c r="Z22" s="2">
+      <c r="AA22" s="2">
         <v>4.2</v>
       </c>
-      <c r="AA22" s="2">
+      <c r="AB22" s="2">
         <v>3.3</v>
       </c>
-      <c r="AB22" s="2">
+      <c r="AC22" s="2">
         <v>1</v>
       </c>
-      <c r="AC22" s="2">
+      <c r="AD22" s="2">
         <v>1.1000000000000001</v>
       </c>
-      <c r="AD22" s="2">
+      <c r="AE22" s="2">
         <v>2.5</v>
       </c>
-      <c r="AE22" s="2">
+      <c r="AF22" s="2">
         <v>2.9</v>
       </c>
-      <c r="AF22" s="2">
+      <c r="AG22" s="2">
         <v>19.399999999999999</v>
       </c>
     </row>
-    <row r="23" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>38</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B23" s="5">
+        <v>1</v>
+      </c>
+      <c r="C23" t="s">
         <v>29</v>
       </c>
-      <c r="C23">
+      <c r="D23">
         <v>24</v>
       </c>
-      <c r="D23">
+      <c r="E23">
         <v>16</v>
       </c>
-      <c r="E23">
+      <c r="F23">
         <v>4</v>
       </c>
-      <c r="F23" t="s">
+      <c r="G23" t="s">
         <v>94</v>
       </c>
-      <c r="G23" s="2" t="s">
+      <c r="H23" s="2" t="s">
         <v>86</v>
-      </c>
-      <c r="H23" s="2">
-        <v>39</v>
       </c>
       <c r="I23" s="2">
         <v>39</v>
       </c>
       <c r="J23" s="2">
+        <v>39</v>
+      </c>
+      <c r="K23" s="2">
         <v>34.200000000000003</v>
       </c>
-      <c r="K23" s="2">
+      <c r="L23" s="2">
         <v>7.5</v>
       </c>
-      <c r="L23" s="2">
+      <c r="M23" s="2">
         <v>14.9</v>
       </c>
-      <c r="M23" s="2">
+      <c r="N23" s="2">
         <v>0.505</v>
       </c>
-      <c r="N23" s="2">
+      <c r="O23" s="2">
         <v>1.1000000000000001</v>
       </c>
-      <c r="O23" s="2">
+      <c r="P23" s="2">
         <v>3.3</v>
       </c>
-      <c r="P23" s="2">
+      <c r="Q23" s="2">
         <v>0.34399999999999997</v>
       </c>
-      <c r="Q23" s="2">
+      <c r="R23" s="2">
         <v>6.4</v>
       </c>
-      <c r="R23" s="2">
+      <c r="S23" s="2">
         <v>11.6</v>
       </c>
-      <c r="S23" s="2">
+      <c r="T23" s="2">
         <v>0.55100000000000005</v>
       </c>
-      <c r="T23" s="2">
+      <c r="U23" s="2">
         <v>0.54300000000000004</v>
       </c>
-      <c r="U23" s="2">
+      <c r="V23" s="2">
         <v>3.2</v>
       </c>
-      <c r="V23" s="2">
+      <c r="W23" s="2">
         <v>3.8</v>
       </c>
-      <c r="W23" s="2">
+      <c r="X23" s="2">
         <v>0.83699999999999997</v>
       </c>
-      <c r="X23" s="2">
+      <c r="Y23" s="2">
         <v>2.2999999999999998</v>
       </c>
-      <c r="Y23" s="2">
+      <c r="Z23" s="2">
         <v>6.2</v>
       </c>
-      <c r="Z23" s="2">
+      <c r="AA23" s="2">
         <v>8.4</v>
       </c>
-      <c r="AA23" s="2">
+      <c r="AB23" s="2">
         <v>5.3</v>
       </c>
-      <c r="AB23" s="2">
+      <c r="AC23" s="2">
         <v>1.3</v>
       </c>
-      <c r="AC23" s="2">
+      <c r="AD23" s="2">
         <v>1.4</v>
       </c>
-      <c r="AD23" s="2">
+      <c r="AE23" s="2">
         <v>2.6</v>
       </c>
-      <c r="AE23" s="2">
+      <c r="AF23" s="2">
         <v>2.8</v>
       </c>
-      <c r="AF23" s="2">
+      <c r="AG23" s="2">
         <v>19.399999999999999</v>
       </c>
     </row>
-    <row r="24" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>39</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B24" s="5">
+        <v>1</v>
+      </c>
+      <c r="C24" t="s">
         <v>40</v>
       </c>
-      <c r="C24">
+      <c r="D24">
         <v>10</v>
       </c>
-      <c r="D24">
+      <c r="E24">
         <v>28</v>
       </c>
-      <c r="E24">
+      <c r="F24">
         <v>14</v>
       </c>
-      <c r="G24" s="2" t="s">
+      <c r="H24" s="2" t="s">
         <v>90</v>
-      </c>
-      <c r="H24" s="2">
-        <v>10</v>
       </c>
       <c r="I24" s="2">
         <v>10</v>
       </c>
       <c r="J24" s="2">
+        <v>10</v>
+      </c>
+      <c r="K24" s="2">
         <v>28</v>
       </c>
-      <c r="K24" s="2">
+      <c r="L24" s="2">
         <v>5.6</v>
       </c>
-      <c r="L24" s="2">
+      <c r="M24" s="2">
         <v>13.5</v>
       </c>
-      <c r="M24" s="2">
+      <c r="N24" s="2">
         <v>0.41499999999999998</v>
       </c>
-      <c r="N24" s="2">
+      <c r="O24" s="2">
         <v>1.8</v>
       </c>
-      <c r="O24" s="2">
+      <c r="P24" s="2">
         <v>5.9</v>
       </c>
-      <c r="P24" s="2">
+      <c r="Q24" s="2">
         <v>0.30499999999999999</v>
       </c>
-      <c r="Q24" s="2">
+      <c r="R24" s="2">
         <v>3.8</v>
       </c>
-      <c r="R24" s="2">
+      <c r="S24" s="2">
         <v>7.6</v>
       </c>
-      <c r="S24" s="2">
+      <c r="T24" s="2">
         <v>0.5</v>
       </c>
-      <c r="T24" s="2">
+      <c r="U24" s="2">
         <v>0.48099999999999998</v>
       </c>
-      <c r="U24" s="2">
+      <c r="V24" s="2">
         <v>6.3</v>
       </c>
-      <c r="V24" s="2">
+      <c r="W24" s="2">
         <v>7.3</v>
       </c>
-      <c r="W24" s="2">
+      <c r="X24" s="2">
         <v>0.86299999999999999</v>
       </c>
-      <c r="X24" s="2">
+      <c r="Y24" s="2">
         <v>0</v>
-      </c>
-      <c r="Y24" s="2">
-        <v>1.5</v>
       </c>
       <c r="Z24" s="2">
         <v>1.5</v>
       </c>
       <c r="AA24" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="AB24" s="2">
         <v>8.9</v>
       </c>
-      <c r="AB24" s="2">
+      <c r="AC24" s="2">
         <v>1</v>
       </c>
-      <c r="AC24" s="2">
+      <c r="AD24" s="2">
         <v>0.1</v>
       </c>
-      <c r="AD24" s="2">
+      <c r="AE24" s="2">
         <v>2.6</v>
       </c>
-      <c r="AE24" s="2">
+      <c r="AF24" s="2">
         <v>2</v>
       </c>
-      <c r="AF24" s="2">
+      <c r="AG24" s="2">
         <v>19.3</v>
       </c>
     </row>
-    <row r="25" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>41</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B25" s="5">
+        <v>1</v>
+      </c>
+      <c r="C25" t="s">
         <v>26</v>
       </c>
-      <c r="C25">
+      <c r="D25">
         <v>22</v>
       </c>
-      <c r="D25">
+      <c r="E25">
         <v>18</v>
       </c>
-      <c r="E25">
+      <c r="F25">
         <v>6</v>
       </c>
-      <c r="F25" t="s">
+      <c r="G25" t="s">
         <v>94</v>
       </c>
-      <c r="G25" s="2" t="s">
+      <c r="H25" s="2" t="s">
         <v>93</v>
-      </c>
-      <c r="H25" s="2">
-        <v>40</v>
       </c>
       <c r="I25" s="2">
         <v>40</v>
       </c>
       <c r="J25" s="2">
+        <v>40</v>
+      </c>
+      <c r="K25" s="2">
         <v>33.799999999999997</v>
       </c>
-      <c r="K25" s="2">
+      <c r="L25" s="2">
         <v>7</v>
       </c>
-      <c r="L25" s="2">
+      <c r="M25" s="2">
         <v>15.4</v>
       </c>
-      <c r="M25" s="2">
+      <c r="N25" s="2">
         <v>0.45200000000000001</v>
       </c>
-      <c r="N25" s="2">
+      <c r="O25" s="2">
         <v>1.7</v>
       </c>
-      <c r="O25" s="2">
+      <c r="P25" s="2">
         <v>5</v>
       </c>
-      <c r="P25" s="2">
+      <c r="Q25" s="2">
         <v>0.33800000000000002</v>
       </c>
-      <c r="Q25" s="2">
+      <c r="R25" s="2">
         <v>5.3</v>
       </c>
-      <c r="R25" s="2">
+      <c r="S25" s="2">
         <v>10.5</v>
-      </c>
-      <c r="S25" s="2">
-        <v>0.50600000000000001</v>
       </c>
       <c r="T25" s="2">
         <v>0.50600000000000001</v>
       </c>
       <c r="U25" s="2">
+        <v>0.50600000000000001</v>
+      </c>
+      <c r="V25" s="2">
         <v>3.6</v>
       </c>
-      <c r="V25" s="2">
+      <c r="W25" s="2">
         <v>3.9</v>
       </c>
-      <c r="W25" s="2">
+      <c r="X25" s="2">
         <v>0.92900000000000005</v>
       </c>
-      <c r="X25" s="2">
+      <c r="Y25" s="2">
         <v>1.3</v>
       </c>
-      <c r="Y25" s="2">
+      <c r="Z25" s="2">
         <v>3.3</v>
       </c>
-      <c r="Z25" s="2">
+      <c r="AA25" s="2">
         <v>4.5999999999999996</v>
       </c>
-      <c r="AA25" s="2">
+      <c r="AB25" s="2">
         <v>4.5</v>
       </c>
-      <c r="AB25" s="2">
+      <c r="AC25" s="2">
         <v>0.8</v>
       </c>
-      <c r="AC25" s="2">
+      <c r="AD25" s="2">
         <v>0.5</v>
       </c>
-      <c r="AD25" s="2">
+      <c r="AE25" s="2">
         <v>2.2000000000000002</v>
       </c>
-      <c r="AE25" s="2">
+      <c r="AF25" s="2">
         <v>3</v>
       </c>
-      <c r="AF25" s="2">
+      <c r="AG25" s="2">
         <v>19.2</v>
       </c>
     </row>
-    <row r="26" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>42</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B26" s="5">
+        <v>1</v>
+      </c>
+      <c r="C26" t="s">
         <v>43</v>
       </c>
-      <c r="C26">
+      <c r="D26">
         <v>18</v>
       </c>
-      <c r="D26">
+      <c r="E26">
         <v>20</v>
       </c>
-      <c r="E26">
+      <c r="F26">
         <v>10</v>
       </c>
-      <c r="G26" s="2" t="s">
+      <c r="H26" s="2" t="s">
         <v>90</v>
-      </c>
-      <c r="H26" s="2">
-        <v>30</v>
       </c>
       <c r="I26" s="2">
         <v>30</v>
       </c>
       <c r="J26" s="2">
+        <v>30</v>
+      </c>
+      <c r="K26" s="2">
         <v>32.799999999999997</v>
       </c>
-      <c r="K26" s="2">
+      <c r="L26" s="2">
         <v>6.7</v>
       </c>
-      <c r="L26" s="2">
+      <c r="M26" s="2">
         <v>14.3</v>
       </c>
-      <c r="M26" s="2">
+      <c r="N26" s="2">
         <v>0.46600000000000003</v>
       </c>
-      <c r="N26" s="2">
+      <c r="O26" s="2">
         <v>1.9</v>
       </c>
-      <c r="O26" s="2">
+      <c r="P26" s="2">
         <v>4.8</v>
       </c>
-      <c r="P26" s="2">
+      <c r="Q26" s="2">
         <v>0.38600000000000001</v>
       </c>
-      <c r="Q26" s="2">
+      <c r="R26" s="2">
         <v>4.8</v>
       </c>
-      <c r="R26" s="2">
+      <c r="S26" s="2">
         <v>9.5</v>
       </c>
-      <c r="S26" s="2">
+      <c r="T26" s="2">
         <v>0.50700000000000001</v>
       </c>
-      <c r="T26" s="2">
+      <c r="U26" s="2">
         <v>0.53100000000000003</v>
       </c>
-      <c r="U26" s="2">
+      <c r="V26" s="2">
         <v>4</v>
       </c>
-      <c r="V26" s="2">
+      <c r="W26" s="2">
         <v>5.3</v>
       </c>
-      <c r="W26" s="2">
+      <c r="X26" s="2">
         <v>0.76100000000000001</v>
       </c>
-      <c r="X26" s="2">
+      <c r="Y26" s="2">
         <v>1.2</v>
       </c>
-      <c r="Y26" s="2">
+      <c r="Z26" s="2">
         <v>7.8</v>
       </c>
-      <c r="Z26" s="2">
+      <c r="AA26" s="2">
         <v>8.9</v>
       </c>
-      <c r="AA26" s="2">
+      <c r="AB26" s="2">
         <v>9</v>
       </c>
-      <c r="AB26" s="2">
+      <c r="AC26" s="2">
         <v>0.9</v>
       </c>
-      <c r="AC26" s="2">
+      <c r="AD26" s="2">
         <v>0.4</v>
       </c>
-      <c r="AD26" s="2">
+      <c r="AE26" s="2">
         <v>3.6</v>
       </c>
-      <c r="AE26" s="2">
+      <c r="AF26" s="2">
         <v>1.8</v>
       </c>
-      <c r="AF26" s="2">
+      <c r="AG26" s="2">
         <v>19.2</v>
       </c>
     </row>
-    <row r="27" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>44</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B27" s="5">
+        <v>1</v>
+      </c>
+      <c r="C27" t="s">
         <v>34</v>
       </c>
-      <c r="C27">
+      <c r="D27">
         <v>14</v>
       </c>
-      <c r="D27">
+      <c r="E27">
         <v>25</v>
       </c>
-      <c r="E27">
+      <c r="F27">
         <v>12</v>
       </c>
-      <c r="G27" s="2" t="s">
+      <c r="H27" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="H27" s="2">
+      <c r="I27" s="2">
         <v>38</v>
       </c>
-      <c r="I27" s="2">
+      <c r="J27" s="2">
         <v>37</v>
       </c>
-      <c r="J27" s="2">
+      <c r="K27" s="2">
         <v>32.5</v>
       </c>
-      <c r="K27" s="2">
+      <c r="L27" s="2">
         <v>6.6</v>
       </c>
-      <c r="L27" s="2">
+      <c r="M27" s="2">
         <v>13.8</v>
       </c>
-      <c r="M27" s="2">
+      <c r="N27" s="2">
         <v>0.47599999999999998</v>
       </c>
-      <c r="N27" s="2">
+      <c r="O27" s="2">
         <v>3.5</v>
       </c>
-      <c r="O27" s="2">
+      <c r="P27" s="2">
         <v>8.1999999999999993</v>
       </c>
-      <c r="P27" s="2">
+      <c r="Q27" s="2">
         <v>0.42899999999999999</v>
       </c>
-      <c r="Q27" s="2">
+      <c r="R27" s="2">
         <v>3</v>
       </c>
-      <c r="R27" s="2">
+      <c r="S27" s="2">
         <v>5.6</v>
       </c>
-      <c r="S27" s="2">
+      <c r="T27" s="2">
         <v>0.54500000000000004</v>
       </c>
-      <c r="T27" s="2">
+      <c r="U27" s="2">
         <v>0.60399999999999998</v>
       </c>
-      <c r="U27" s="2">
+      <c r="V27" s="2">
         <v>2.4</v>
       </c>
-      <c r="V27" s="2">
+      <c r="W27" s="2">
         <v>2.8</v>
       </c>
-      <c r="W27" s="2">
+      <c r="X27" s="2">
         <v>0.88600000000000001</v>
       </c>
-      <c r="X27" s="2">
+      <c r="Y27" s="2">
         <v>1</v>
       </c>
-      <c r="Y27" s="2">
+      <c r="Z27" s="2">
         <v>4.0999999999999996</v>
       </c>
-      <c r="Z27" s="2">
+      <c r="AA27" s="2">
         <v>5.0999999999999996</v>
       </c>
-      <c r="AA27" s="2">
+      <c r="AB27" s="2">
         <v>3.6</v>
       </c>
-      <c r="AB27" s="2">
+      <c r="AC27" s="2">
         <v>0.7</v>
       </c>
-      <c r="AC27" s="2">
+      <c r="AD27" s="2">
         <v>0.2</v>
       </c>
-      <c r="AD27" s="2">
+      <c r="AE27" s="2">
         <v>2.2999999999999998</v>
       </c>
-      <c r="AE27" s="2">
+      <c r="AF27" s="2">
         <v>2.4</v>
       </c>
-      <c r="AF27" s="2">
+      <c r="AG27" s="2">
         <v>19.100000000000001</v>
       </c>
     </row>
-    <row r="28" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>45</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B28" s="5">
+        <v>1</v>
+      </c>
+      <c r="C28" t="s">
         <v>17</v>
       </c>
-      <c r="C28">
+      <c r="D28">
         <v>11</v>
       </c>
-      <c r="D28">
+      <c r="E28">
         <v>25</v>
       </c>
-      <c r="E28">
+      <c r="F28">
         <v>13</v>
       </c>
-      <c r="G28" s="2" t="s">
+      <c r="H28" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="H28" s="2">
+      <c r="I28" s="2">
         <v>15</v>
       </c>
-      <c r="I28" s="2">
+      <c r="J28" s="2">
         <v>8</v>
       </c>
-      <c r="J28" s="2">
+      <c r="K28" s="2">
         <v>25.3</v>
       </c>
-      <c r="K28" s="2">
+      <c r="L28" s="2">
         <v>6.1</v>
       </c>
-      <c r="L28" s="2">
+      <c r="M28" s="2">
         <v>14.5</v>
       </c>
-      <c r="M28" s="2">
+      <c r="N28" s="2">
         <v>0.42199999999999999</v>
       </c>
-      <c r="N28" s="2">
+      <c r="O28" s="2">
         <v>1.9</v>
       </c>
-      <c r="O28" s="2">
+      <c r="P28" s="2">
         <v>5.3</v>
       </c>
-      <c r="P28" s="2">
+      <c r="Q28" s="2">
         <v>0.35</v>
       </c>
-      <c r="Q28" s="2">
+      <c r="R28" s="2">
         <v>4.3</v>
       </c>
-      <c r="R28" s="2">
+      <c r="S28" s="2">
         <v>9.1999999999999993</v>
       </c>
-      <c r="S28" s="2">
+      <c r="T28" s="2">
         <v>0.46400000000000002</v>
       </c>
-      <c r="T28" s="2">
+      <c r="U28" s="2">
         <v>0.48599999999999999</v>
       </c>
-      <c r="U28" s="2">
+      <c r="V28" s="2">
         <v>4.8</v>
       </c>
-      <c r="V28" s="2">
+      <c r="W28" s="2">
         <v>5.6</v>
       </c>
-      <c r="W28" s="2">
+      <c r="X28" s="2">
         <v>0.85699999999999998</v>
       </c>
-      <c r="X28" s="2">
+      <c r="Y28" s="2">
         <v>0.4</v>
       </c>
-      <c r="Y28" s="2">
+      <c r="Z28" s="2">
         <v>1.4</v>
       </c>
-      <c r="Z28" s="2">
+      <c r="AA28" s="2">
         <v>1.8</v>
       </c>
-      <c r="AA28" s="2">
+      <c r="AB28" s="2">
         <v>2.5</v>
       </c>
-      <c r="AB28" s="2">
+      <c r="AC28" s="2">
         <v>0.3</v>
       </c>
-      <c r="AC28" s="2">
+      <c r="AD28" s="2">
         <v>0.1</v>
       </c>
-      <c r="AD28" s="2">
+      <c r="AE28" s="2">
         <v>2.1</v>
       </c>
-      <c r="AE28" s="2">
+      <c r="AF28" s="2">
         <v>1.5</v>
       </c>
-      <c r="AF28" s="2">
+      <c r="AG28" s="2">
         <v>18.899999999999999</v>
       </c>
     </row>
-    <row r="29" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>46</v>
       </c>
-      <c r="B29" t="s">
+      <c r="B29" s="5">
+        <v>1</v>
+      </c>
+      <c r="C29" t="s">
         <v>22</v>
       </c>
-      <c r="C29">
+      <c r="D29">
         <v>20</v>
       </c>
-      <c r="D29">
+      <c r="E29">
         <v>21</v>
       </c>
-      <c r="E29">
+      <c r="F29">
         <v>9</v>
       </c>
-      <c r="G29" s="2" t="s">
+      <c r="H29" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="H29" s="2">
+      <c r="I29" s="2">
         <v>36</v>
       </c>
-      <c r="I29" s="2">
+      <c r="J29" s="2">
         <v>35</v>
       </c>
-      <c r="J29" s="2">
+      <c r="K29" s="2">
         <v>30.7</v>
       </c>
-      <c r="K29" s="2">
+      <c r="L29" s="2">
         <v>6.8</v>
       </c>
-      <c r="L29" s="2">
+      <c r="M29" s="2">
         <v>15.1</v>
       </c>
-      <c r="M29" s="2">
+      <c r="N29" s="2">
         <v>0.45100000000000001</v>
       </c>
-      <c r="N29" s="2">
+      <c r="O29" s="2">
         <v>2.7</v>
       </c>
-      <c r="O29" s="2">
+      <c r="P29" s="2">
         <v>6.9</v>
       </c>
-      <c r="P29" s="2">
+      <c r="Q29" s="2">
         <v>0.38700000000000001</v>
       </c>
-      <c r="Q29" s="2">
+      <c r="R29" s="2">
         <v>4.0999999999999996</v>
       </c>
-      <c r="R29" s="2">
+      <c r="S29" s="2">
         <v>8.1999999999999993</v>
       </c>
-      <c r="S29" s="2">
+      <c r="T29" s="2">
         <v>0.505</v>
       </c>
-      <c r="T29" s="2">
+      <c r="U29" s="2">
         <v>0.54</v>
       </c>
-      <c r="U29" s="2">
+      <c r="V29" s="2">
         <v>2.2999999999999998</v>
       </c>
-      <c r="V29" s="2">
+      <c r="W29" s="2">
         <v>2.9</v>
       </c>
-      <c r="W29" s="2">
+      <c r="X29" s="2">
         <v>0.79200000000000004</v>
       </c>
-      <c r="X29" s="2">
+      <c r="Y29" s="2">
         <v>0.6</v>
       </c>
-      <c r="Y29" s="2">
+      <c r="Z29" s="2">
         <v>2.8</v>
       </c>
-      <c r="Z29" s="2">
+      <c r="AA29" s="2">
         <v>3.4</v>
       </c>
-      <c r="AA29" s="2">
+      <c r="AB29" s="2">
         <v>3.6</v>
       </c>
-      <c r="AB29" s="2">
+      <c r="AC29" s="2">
         <v>0.7</v>
       </c>
-      <c r="AC29" s="2">
+      <c r="AD29" s="2">
         <v>0.3</v>
       </c>
-      <c r="AD29" s="2">
+      <c r="AE29" s="2">
         <v>1.6</v>
       </c>
-      <c r="AE29" s="2">
+      <c r="AF29" s="2">
         <v>2.1</v>
       </c>
-      <c r="AF29" s="2">
+      <c r="AG29" s="2">
         <v>18.600000000000001</v>
       </c>
     </row>
-    <row r="30" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>47</v>
       </c>
-      <c r="B30" t="s">
+      <c r="B30" s="5">
+        <v>1</v>
+      </c>
+      <c r="C30" t="s">
         <v>43</v>
       </c>
-      <c r="C30">
+      <c r="D30">
         <v>18</v>
       </c>
-      <c r="D30">
+      <c r="E30">
         <v>20</v>
       </c>
-      <c r="E30">
+      <c r="F30">
         <v>10</v>
       </c>
-      <c r="G30" s="2" t="s">
+      <c r="H30" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="H30" s="2">
+      <c r="I30" s="2">
         <v>18</v>
       </c>
-      <c r="I30" s="2">
+      <c r="J30" s="2">
         <v>15</v>
       </c>
-      <c r="J30" s="2">
+      <c r="K30" s="2">
         <v>28</v>
       </c>
-      <c r="K30" s="2">
+      <c r="L30" s="2">
         <v>6</v>
       </c>
-      <c r="L30" s="2">
+      <c r="M30" s="2">
         <v>13.3</v>
       </c>
-      <c r="M30" s="2">
+      <c r="N30" s="2">
         <v>0.45</v>
       </c>
-      <c r="N30" s="2">
+      <c r="O30" s="2">
         <v>2.1</v>
       </c>
-      <c r="O30" s="2">
+      <c r="P30" s="2">
         <v>6.7</v>
       </c>
-      <c r="P30" s="2">
+      <c r="Q30" s="2">
         <v>0.317</v>
       </c>
-      <c r="Q30" s="2">
+      <c r="R30" s="2">
         <v>3.9</v>
       </c>
-      <c r="R30" s="2">
+      <c r="S30" s="2">
         <v>6.7</v>
       </c>
-      <c r="S30" s="2">
+      <c r="T30" s="2">
         <v>0.58299999999999996</v>
       </c>
-      <c r="T30" s="2">
+      <c r="U30" s="2">
         <v>0.52900000000000003</v>
       </c>
-      <c r="U30" s="2">
+      <c r="V30" s="2">
         <v>4.4000000000000004</v>
       </c>
-      <c r="V30" s="2">
+      <c r="W30" s="2">
         <v>5.6</v>
       </c>
-      <c r="W30" s="2">
+      <c r="X30" s="2">
         <v>0.8</v>
       </c>
-      <c r="X30" s="2">
+      <c r="Y30" s="2">
         <v>0.3</v>
       </c>
-      <c r="Y30" s="2">
+      <c r="Z30" s="2">
         <v>3.1</v>
       </c>
-      <c r="Z30" s="2">
+      <c r="AA30" s="2">
         <v>3.4</v>
       </c>
-      <c r="AA30" s="2">
+      <c r="AB30" s="2">
         <v>4.5</v>
       </c>
-      <c r="AB30" s="2">
+      <c r="AC30" s="2">
         <v>0.7</v>
       </c>
-      <c r="AC30" s="2">
+      <c r="AD30" s="2">
         <v>0</v>
       </c>
-      <c r="AD30" s="2">
+      <c r="AE30" s="2">
         <v>3</v>
       </c>
-      <c r="AE30" s="2">
+      <c r="AF30" s="2">
         <v>2.2999999999999998</v>
       </c>
-      <c r="AF30" s="2">
+      <c r="AG30" s="2">
         <v>18.600000000000001</v>
       </c>
-      <c r="AG30" s="2"/>
+      <c r="AH30" s="2"/>
     </row>
-    <row r="31" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>48</v>
       </c>
-      <c r="B31" t="s">
+      <c r="B31" s="5">
+        <v>1</v>
+      </c>
+      <c r="C31" t="s">
         <v>7</v>
       </c>
-      <c r="C31">
+      <c r="D31">
         <v>24</v>
       </c>
-      <c r="D31">
+      <c r="E31">
         <v>14</v>
       </c>
-      <c r="E31">
+      <c r="F31">
         <v>3</v>
       </c>
-      <c r="G31" s="2" t="s">
+      <c r="H31" s="2" t="s">
         <v>93</v>
-      </c>
-      <c r="H31" s="2">
-        <v>37</v>
       </c>
       <c r="I31" s="2">
         <v>37</v>
       </c>
       <c r="J31" s="2">
+        <v>37</v>
+      </c>
+      <c r="K31" s="2">
         <v>34.200000000000003</v>
       </c>
-      <c r="K31" s="2">
+      <c r="L31" s="2">
         <v>6.4</v>
       </c>
-      <c r="L31" s="2">
+      <c r="M31" s="2">
         <v>16.100000000000001</v>
       </c>
-      <c r="M31" s="2">
+      <c r="N31" s="2">
         <v>0.39900000000000002</v>
       </c>
-      <c r="N31" s="2">
+      <c r="O31" s="2">
         <v>3.2</v>
       </c>
-      <c r="O31" s="2">
+      <c r="P31" s="2">
         <v>9.6</v>
       </c>
-      <c r="P31" s="2">
+      <c r="Q31" s="2">
         <v>0.33300000000000002</v>
       </c>
-      <c r="Q31" s="2">
+      <c r="R31" s="2">
         <v>3.2</v>
       </c>
-      <c r="R31" s="2">
+      <c r="S31" s="2">
         <v>6.5</v>
       </c>
-      <c r="S31" s="2">
+      <c r="T31" s="2">
         <v>0.498</v>
       </c>
-      <c r="T31" s="2">
+      <c r="U31" s="2">
         <v>0.499</v>
       </c>
-      <c r="U31" s="2">
+      <c r="V31" s="2">
         <v>2.6</v>
       </c>
-      <c r="V31" s="2">
+      <c r="W31" s="2">
         <v>2.9</v>
       </c>
-      <c r="W31" s="2">
+      <c r="X31" s="2">
         <v>0.88</v>
       </c>
-      <c r="X31" s="2">
+      <c r="Y31" s="2">
         <v>0.8</v>
       </c>
-      <c r="Y31" s="2">
+      <c r="Z31" s="2">
         <v>3.6</v>
       </c>
-      <c r="Z31" s="2">
+      <c r="AA31" s="2">
         <v>4.4000000000000004</v>
       </c>
-      <c r="AA31" s="2">
+      <c r="AB31" s="2">
         <v>5.2</v>
       </c>
-      <c r="AB31" s="2">
+      <c r="AC31" s="2">
         <v>1.4</v>
       </c>
-      <c r="AC31" s="2">
+      <c r="AD31" s="2">
         <v>1.6</v>
       </c>
-      <c r="AD31" s="2">
+      <c r="AE31" s="2">
         <v>1.8</v>
       </c>
-      <c r="AE31" s="2">
+      <c r="AF31" s="2">
         <v>1.7</v>
       </c>
-      <c r="AF31" s="2">
+      <c r="AG31" s="2">
         <v>18.600000000000001</v>
       </c>
     </row>
-    <row r="32" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>49</v>
       </c>
-      <c r="B32" t="s">
+      <c r="B32" s="5">
+        <v>1</v>
+      </c>
+      <c r="C32" t="s">
         <v>11</v>
       </c>
-      <c r="C32">
+      <c r="D32">
         <v>17</v>
       </c>
-      <c r="D32">
+      <c r="E32">
         <v>22</v>
       </c>
-      <c r="E32">
+      <c r="F32">
         <v>11</v>
       </c>
-      <c r="G32" s="2" t="s">
+      <c r="H32" s="2" t="s">
         <v>90</v>
-      </c>
-      <c r="H32" s="2">
-        <v>20</v>
       </c>
       <c r="I32" s="2">
         <v>20</v>
       </c>
       <c r="J32" s="2">
+        <v>20</v>
+      </c>
+      <c r="K32" s="2">
         <v>34.700000000000003</v>
       </c>
-      <c r="K32" s="2">
+      <c r="L32" s="2">
         <v>6.3</v>
       </c>
-      <c r="L32" s="2">
+      <c r="M32" s="2">
         <v>13.8</v>
       </c>
-      <c r="M32" s="2">
+      <c r="N32" s="2">
         <v>0.45800000000000002</v>
       </c>
-      <c r="N32" s="2">
+      <c r="O32" s="2">
         <v>1.8</v>
       </c>
-      <c r="O32" s="2">
+      <c r="P32" s="2">
         <v>4.9000000000000004</v>
       </c>
-      <c r="P32" s="2">
+      <c r="Q32" s="2">
         <v>0.36699999999999999</v>
       </c>
-      <c r="Q32" s="2">
+      <c r="R32" s="2">
         <v>4.5</v>
       </c>
-      <c r="R32" s="2">
+      <c r="S32" s="2">
         <v>8.9</v>
       </c>
-      <c r="S32" s="2">
+      <c r="T32" s="2">
         <v>0.50800000000000001</v>
       </c>
-      <c r="T32" s="2">
+      <c r="U32" s="2">
         <v>0.52400000000000002</v>
       </c>
-      <c r="U32" s="2">
+      <c r="V32" s="2">
         <v>3.8</v>
       </c>
-      <c r="V32" s="2">
+      <c r="W32" s="2">
         <v>4.5</v>
       </c>
-      <c r="W32" s="2">
+      <c r="X32" s="2">
         <v>0.84399999999999997</v>
       </c>
-      <c r="X32" s="2">
+      <c r="Y32" s="2">
         <v>0.8</v>
       </c>
-      <c r="Y32" s="2">
+      <c r="Z32" s="2">
         <v>4.5</v>
       </c>
-      <c r="Z32" s="2">
+      <c r="AA32" s="2">
         <v>5.3</v>
       </c>
-      <c r="AA32" s="2">
+      <c r="AB32" s="2">
         <v>7.7</v>
       </c>
-      <c r="AB32" s="2">
+      <c r="AC32" s="2">
         <v>2.2999999999999998</v>
       </c>
-      <c r="AC32" s="2">
+      <c r="AD32" s="2">
         <v>0.4</v>
       </c>
-      <c r="AD32" s="2">
+      <c r="AE32" s="2">
         <v>3.4</v>
       </c>
-      <c r="AE32" s="2">
+      <c r="AF32" s="2">
         <v>2.1</v>
       </c>
-      <c r="AF32" s="2">
+      <c r="AG32" s="2">
         <v>18.2</v>
       </c>
-      <c r="AG32" s="2"/>
+      <c r="AH32" s="2"/>
     </row>
-    <row r="33" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>50</v>
       </c>
-      <c r="B33" t="s">
+      <c r="B33" s="5">
+        <v>1</v>
+      </c>
+      <c r="C33" t="s">
         <v>15</v>
       </c>
-      <c r="C33">
+      <c r="D33">
         <v>28</v>
       </c>
-      <c r="D33">
+      <c r="E33">
         <v>10</v>
       </c>
-      <c r="E33">
+      <c r="F33">
         <v>1</v>
       </c>
-      <c r="G33" s="2" t="s">
+      <c r="H33" s="2" t="s">
         <v>91</v>
-      </c>
-      <c r="H33" s="2">
-        <v>31</v>
       </c>
       <c r="I33" s="2">
         <v>31</v>
       </c>
       <c r="J33" s="2">
+        <v>31</v>
+      </c>
+      <c r="K33" s="2">
         <v>28.4</v>
       </c>
-      <c r="K33" s="2">
+      <c r="L33" s="2">
         <v>7</v>
       </c>
-      <c r="L33" s="2">
+      <c r="M33" s="2">
         <v>11</v>
       </c>
-      <c r="M33" s="2">
+      <c r="N33" s="2">
         <v>0.63300000000000001</v>
-      </c>
-      <c r="N33" s="2">
-        <v>0</v>
       </c>
       <c r="O33" s="2">
         <v>0</v>
       </c>
-      <c r="P33" s="2"/>
-      <c r="Q33" s="2">
+      <c r="P33" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q33" s="2"/>
+      <c r="R33" s="2">
         <v>7</v>
       </c>
-      <c r="R33" s="2">
+      <c r="S33" s="2">
         <v>11</v>
-      </c>
-      <c r="S33" s="2">
-        <v>0.63300000000000001</v>
       </c>
       <c r="T33" s="2">
         <v>0.63300000000000001</v>
       </c>
       <c r="U33" s="2">
+        <v>0.63300000000000001</v>
+      </c>
+      <c r="V33" s="2">
         <v>4</v>
       </c>
-      <c r="V33" s="2">
+      <c r="W33" s="2">
         <v>5.5</v>
       </c>
-      <c r="W33" s="2">
+      <c r="X33" s="2">
         <v>0.72399999999999998</v>
       </c>
-      <c r="X33" s="2">
+      <c r="Y33" s="2">
         <v>4.0999999999999996</v>
       </c>
-      <c r="Y33" s="2">
+      <c r="Z33" s="2">
         <v>6.5</v>
       </c>
-      <c r="Z33" s="2">
+      <c r="AA33" s="2">
         <v>10.6</v>
       </c>
-      <c r="AA33" s="2">
+      <c r="AB33" s="2">
         <v>1.7</v>
-      </c>
-      <c r="AB33" s="2">
-        <v>0.9</v>
       </c>
       <c r="AC33" s="2">
         <v>0.9</v>
       </c>
       <c r="AD33" s="2">
+        <v>0.9</v>
+      </c>
+      <c r="AE33" s="2">
         <v>2.2999999999999998</v>
       </c>
-      <c r="AE33" s="2">
+      <c r="AF33" s="2">
         <v>3.2</v>
       </c>
-      <c r="AF33" s="2">
+      <c r="AG33" s="2">
         <v>17.899999999999999</v>
       </c>
     </row>
-    <row r="34" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>51</v>
       </c>
-      <c r="B34" t="s">
+      <c r="B34" s="5">
+        <v>1</v>
+      </c>
+      <c r="C34" t="s">
         <v>9</v>
       </c>
-      <c r="C34">
+      <c r="D34">
         <v>22</v>
       </c>
-      <c r="D34">
+      <c r="E34">
         <v>18</v>
       </c>
-      <c r="E34">
+      <c r="F34">
         <v>7</v>
       </c>
-      <c r="G34" s="2" t="s">
+      <c r="H34" s="2" t="s">
         <v>90</v>
-      </c>
-      <c r="H34" s="2">
-        <v>24</v>
       </c>
       <c r="I34" s="2">
         <v>24</v>
       </c>
       <c r="J34" s="2">
+        <v>24</v>
+      </c>
+      <c r="K34" s="2">
         <v>30.6</v>
       </c>
-      <c r="K34" s="2">
+      <c r="L34" s="2">
         <v>6.5</v>
       </c>
-      <c r="L34" s="2">
+      <c r="M34" s="2">
         <v>14.5</v>
       </c>
-      <c r="M34" s="2">
+      <c r="N34" s="2">
         <v>0.44700000000000001</v>
       </c>
-      <c r="N34" s="2">
+      <c r="O34" s="2">
         <v>2.1</v>
       </c>
-      <c r="O34" s="2">
+      <c r="P34" s="2">
         <v>6.2</v>
       </c>
-      <c r="P34" s="2">
+      <c r="Q34" s="2">
         <v>0.34499999999999997</v>
       </c>
-      <c r="Q34" s="2">
+      <c r="R34" s="2">
         <v>4.3</v>
       </c>
-      <c r="R34" s="2">
+      <c r="S34" s="2">
         <v>8.3000000000000007</v>
       </c>
-      <c r="S34" s="2">
+      <c r="T34" s="2">
         <v>0.52300000000000002</v>
       </c>
-      <c r="T34" s="2">
+      <c r="U34" s="2">
         <v>0.52</v>
       </c>
-      <c r="U34" s="2">
+      <c r="V34" s="2">
         <v>2.6</v>
       </c>
-      <c r="V34" s="2">
+      <c r="W34" s="2">
         <v>3</v>
       </c>
-      <c r="W34" s="2">
+      <c r="X34" s="2">
         <v>0.86299999999999999</v>
       </c>
-      <c r="X34" s="2">
+      <c r="Y34" s="2">
         <v>0.5</v>
       </c>
-      <c r="Y34" s="2">
+      <c r="Z34" s="2">
         <v>2</v>
       </c>
-      <c r="Z34" s="2">
+      <c r="AA34" s="2">
         <v>2.4</v>
       </c>
-      <c r="AA34" s="2">
+      <c r="AB34" s="2">
         <v>6.9</v>
       </c>
-      <c r="AB34" s="2">
+      <c r="AC34" s="2">
         <v>0.7</v>
       </c>
-      <c r="AC34" s="2">
+      <c r="AD34" s="2">
         <v>0.1</v>
       </c>
-      <c r="AD34" s="2">
+      <c r="AE34" s="2">
         <v>2.8</v>
       </c>
-      <c r="AE34" s="2">
+      <c r="AF34" s="2">
         <v>1.8</v>
       </c>
-      <c r="AF34" s="2">
+      <c r="AG34" s="2">
         <v>17.7</v>
       </c>
     </row>
-    <row r="35" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>52</v>
       </c>
-      <c r="B35" t="s">
+      <c r="B35" s="5">
+        <v>1</v>
+      </c>
+      <c r="C35" t="s">
         <v>9</v>
       </c>
-      <c r="C35">
+      <c r="D35">
         <v>22</v>
       </c>
-      <c r="D35">
+      <c r="E35">
         <v>18</v>
       </c>
-      <c r="E35">
+      <c r="F35">
         <v>7</v>
       </c>
-      <c r="G35" s="2" t="s">
+      <c r="H35" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="H35" s="2">
+      <c r="I35" s="2">
         <v>34</v>
       </c>
-      <c r="I35" s="2">
+      <c r="J35" s="2">
         <v>32</v>
       </c>
-      <c r="J35" s="2">
+      <c r="K35" s="2">
         <v>33.1</v>
       </c>
-      <c r="K35" s="2">
+      <c r="L35" s="2">
         <v>6.9</v>
       </c>
-      <c r="L35" s="2">
+      <c r="M35" s="2">
         <v>13.4</v>
       </c>
-      <c r="M35" s="2">
+      <c r="N35" s="2">
         <v>0.51200000000000001</v>
       </c>
-      <c r="N35" s="2">
+      <c r="O35" s="2">
         <v>1.3</v>
       </c>
-      <c r="O35" s="2">
+      <c r="P35" s="2">
         <v>3.8</v>
       </c>
-      <c r="P35" s="2">
+      <c r="Q35" s="2">
         <v>0.33100000000000002</v>
       </c>
-      <c r="Q35" s="2">
+      <c r="R35" s="2">
         <v>5.6</v>
       </c>
-      <c r="R35" s="2">
+      <c r="S35" s="2">
         <v>9.6</v>
       </c>
-      <c r="S35" s="2">
+      <c r="T35" s="2">
         <v>0.58499999999999996</v>
       </c>
-      <c r="T35" s="2">
+      <c r="U35" s="2">
         <v>0.55900000000000005</v>
       </c>
-      <c r="U35" s="2">
+      <c r="V35" s="2">
         <v>3.1</v>
       </c>
-      <c r="V35" s="2">
+      <c r="W35" s="2">
         <v>4.8</v>
       </c>
-      <c r="W35" s="2">
+      <c r="X35" s="2">
         <v>0.63800000000000001</v>
       </c>
-      <c r="X35" s="2">
+      <c r="Y35" s="2">
         <v>2.4</v>
       </c>
-      <c r="Y35" s="2">
+      <c r="Z35" s="2">
         <v>6.2</v>
       </c>
-      <c r="Z35" s="2">
+      <c r="AA35" s="2">
         <v>8.6</v>
       </c>
-      <c r="AA35" s="2">
+      <c r="AB35" s="2">
         <v>4</v>
       </c>
-      <c r="AB35" s="2">
+      <c r="AC35" s="2">
         <v>0.9</v>
       </c>
-      <c r="AC35" s="2">
+      <c r="AD35" s="2">
         <v>1.8</v>
       </c>
-      <c r="AD35" s="2">
+      <c r="AE35" s="2">
         <v>2.2000000000000002</v>
       </c>
-      <c r="AE35" s="2">
+      <c r="AF35" s="2">
         <v>2.5</v>
       </c>
-      <c r="AF35" s="2">
+      <c r="AG35" s="2">
         <v>18</v>
       </c>
     </row>
-    <row r="36" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>53</v>
       </c>
-      <c r="B36" t="s">
+      <c r="B36" s="5">
+        <v>1</v>
+      </c>
+      <c r="C36" t="s">
         <v>24</v>
       </c>
-      <c r="C36">
+      <c r="D36">
         <v>8</v>
       </c>
-      <c r="D36">
+      <c r="E36">
         <v>31</v>
       </c>
-      <c r="E36">
+      <c r="F36">
         <v>15</v>
       </c>
-      <c r="F36" t="s">
+      <c r="G36" t="s">
         <v>95</v>
       </c>
-      <c r="G36" s="2" t="s">
+      <c r="H36" s="2" t="s">
         <v>92</v>
-      </c>
-      <c r="H36" s="2">
-        <v>24</v>
       </c>
       <c r="I36" s="2">
         <v>24</v>
       </c>
       <c r="J36" s="2">
+        <v>24</v>
+      </c>
+      <c r="K36" s="2">
         <v>32.200000000000003</v>
       </c>
-      <c r="K36" s="2">
+      <c r="L36" s="2">
         <v>5.6</v>
       </c>
-      <c r="L36" s="2">
+      <c r="M36" s="2">
         <v>13.2</v>
       </c>
-      <c r="M36" s="2">
+      <c r="N36" s="2">
         <v>0.42299999999999999</v>
       </c>
-      <c r="N36" s="2">
+      <c r="O36" s="2">
         <v>2.2000000000000002</v>
       </c>
-      <c r="O36" s="2">
+      <c r="P36" s="2">
         <v>6</v>
       </c>
-      <c r="P36" s="2">
+      <c r="Q36" s="2">
         <v>0.36599999999999999</v>
       </c>
-      <c r="Q36" s="2">
+      <c r="R36" s="2">
         <v>3.4</v>
       </c>
-      <c r="R36" s="2">
+      <c r="S36" s="2">
         <v>7.2</v>
       </c>
-      <c r="S36" s="2">
+      <c r="T36" s="2">
         <v>0.47099999999999997</v>
       </c>
-      <c r="T36" s="2">
+      <c r="U36" s="2">
         <v>0.50600000000000001</v>
       </c>
-      <c r="U36" s="2">
+      <c r="V36" s="2">
         <v>4.4000000000000004</v>
       </c>
-      <c r="V36" s="2">
+      <c r="W36" s="2">
         <v>5</v>
       </c>
-      <c r="W36" s="2">
+      <c r="X36" s="2">
         <v>0.876</v>
       </c>
-      <c r="X36" s="2">
+      <c r="Y36" s="2">
         <v>0.8</v>
       </c>
-      <c r="Y36" s="2">
+      <c r="Z36" s="2">
         <v>4.7</v>
       </c>
-      <c r="Z36" s="2">
+      <c r="AA36" s="2">
         <v>5.5</v>
       </c>
-      <c r="AA36" s="2">
+      <c r="AB36" s="2">
         <v>2.2000000000000002</v>
       </c>
-      <c r="AB36" s="2">
+      <c r="AC36" s="2">
         <v>0.7</v>
       </c>
-      <c r="AC36" s="2">
+      <c r="AD36" s="2">
         <v>0.2</v>
       </c>
-      <c r="AD36" s="2">
+      <c r="AE36" s="2">
         <v>2.4</v>
       </c>
-      <c r="AE36" s="2">
+      <c r="AF36" s="2">
         <v>2.9</v>
       </c>
-      <c r="AF36" s="2">
+      <c r="AG36" s="2">
         <v>17.8</v>
       </c>
     </row>
-    <row r="37" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>54</v>
       </c>
-      <c r="B37" t="s">
+      <c r="B37" s="5">
+        <v>1</v>
+      </c>
+      <c r="C37" t="s">
         <v>24</v>
       </c>
-      <c r="C37">
+      <c r="D37">
         <v>8</v>
       </c>
-      <c r="D37">
+      <c r="E37">
         <v>31</v>
       </c>
-      <c r="E37">
+      <c r="F37">
         <v>15</v>
       </c>
-      <c r="F37" t="s">
+      <c r="G37" t="s">
         <v>95</v>
       </c>
-      <c r="G37" s="2" t="s">
+      <c r="H37" s="2" t="s">
         <v>90</v>
-      </c>
-      <c r="H37" s="2">
-        <v>30</v>
       </c>
       <c r="I37" s="2">
         <v>30</v>
       </c>
       <c r="J37" s="2">
+        <v>30</v>
+      </c>
+      <c r="K37" s="2">
         <v>31.7</v>
       </c>
-      <c r="K37" s="2">
+      <c r="L37" s="2">
         <v>6.2</v>
       </c>
-      <c r="L37" s="2">
+      <c r="M37" s="2">
         <v>13.9</v>
       </c>
-      <c r="M37" s="2">
+      <c r="N37" s="2">
         <v>0.44500000000000001</v>
       </c>
-      <c r="N37" s="2">
+      <c r="O37" s="2">
         <v>1.8</v>
       </c>
-      <c r="O37" s="2">
+      <c r="P37" s="2">
         <v>5</v>
       </c>
-      <c r="P37" s="2">
+      <c r="Q37" s="2">
         <v>0.36399999999999999</v>
       </c>
-      <c r="Q37" s="2">
+      <c r="R37" s="2">
         <v>4.3</v>
       </c>
-      <c r="R37" s="2">
+      <c r="S37" s="2">
         <v>8.8000000000000007</v>
       </c>
-      <c r="S37" s="2">
+      <c r="T37" s="2">
         <v>0.49099999999999999</v>
       </c>
-      <c r="T37" s="2">
+      <c r="U37" s="2">
         <v>0.51100000000000001</v>
       </c>
-      <c r="U37" s="2">
+      <c r="V37" s="2">
         <v>3.5</v>
       </c>
-      <c r="V37" s="2">
+      <c r="W37" s="2">
         <v>4.3</v>
       </c>
-      <c r="W37" s="2">
+      <c r="X37" s="2">
         <v>0.80600000000000005</v>
       </c>
-      <c r="X37" s="2">
+      <c r="Y37" s="2">
         <v>0.3</v>
       </c>
-      <c r="Y37" s="2">
+      <c r="Z37" s="2">
         <v>2.2000000000000002</v>
       </c>
-      <c r="Z37" s="2">
+      <c r="AA37" s="2">
         <v>2.5</v>
       </c>
-      <c r="AA37" s="2">
+      <c r="AB37" s="2">
         <v>7</v>
       </c>
-      <c r="AB37" s="2">
+      <c r="AC37" s="2">
         <v>1</v>
       </c>
-      <c r="AC37" s="2">
+      <c r="AD37" s="2">
         <v>0.1</v>
-      </c>
-      <c r="AD37" s="2">
-        <v>2.2999999999999998</v>
       </c>
       <c r="AE37" s="2">
         <v>2.2999999999999998</v>
       </c>
       <c r="AF37" s="2">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="AG37" s="2">
         <v>17.600000000000001</v>
       </c>
     </row>
-    <row r="38" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>55</v>
       </c>
-      <c r="B38" t="s">
+      <c r="B38" s="5">
+        <v>1</v>
+      </c>
+      <c r="C38" t="s">
         <v>40</v>
       </c>
-      <c r="C38">
+      <c r="D38">
         <v>10</v>
       </c>
-      <c r="D38">
+      <c r="E38">
         <v>28</v>
       </c>
-      <c r="E38">
+      <c r="F38">
         <v>14</v>
       </c>
-      <c r="G38" s="2" t="s">
+      <c r="H38" s="2" t="s">
         <v>91</v>
-      </c>
-      <c r="H38" s="2">
-        <v>29</v>
       </c>
       <c r="I38" s="2">
         <v>29</v>
       </c>
       <c r="J38" s="2">
+        <v>29</v>
+      </c>
+      <c r="K38" s="2">
         <v>28.2</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>7</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>13.9</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>0.501</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>1</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>3</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>0.34899999999999998</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>5.9</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>10.9</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>0.54300000000000004</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>0.53800000000000003</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>2.2999999999999998</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>3.3</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>0.70799999999999996</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>2.2000000000000002</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>5.6</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>7.8</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>2.9</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>0.8</v>
       </c>
-      <c r="AC38" s="3">
+      <c r="AD38" s="3">
         <v>2.2999999999999998</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>1.8</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>2</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>17.3</v>
       </c>
     </row>
-    <row r="39" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>56</v>
       </c>
-      <c r="B39" t="s">
+      <c r="B39" s="5">
+        <v>1</v>
+      </c>
+      <c r="C39" t="s">
         <v>22</v>
       </c>
-      <c r="C39">
+      <c r="D39">
         <v>20</v>
       </c>
-      <c r="D39">
+      <c r="E39">
         <v>21</v>
       </c>
-      <c r="E39">
+      <c r="F39">
         <v>9</v>
       </c>
-      <c r="G39" s="2" t="s">
+      <c r="H39" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="H39" s="2">
+      <c r="I39" s="2">
         <v>17</v>
       </c>
-      <c r="I39" s="2">
+      <c r="J39" s="2">
         <v>12</v>
       </c>
-      <c r="J39" s="2">
+      <c r="K39" s="2">
         <v>24.3</v>
       </c>
-      <c r="K39" s="2">
+      <c r="L39" s="2">
         <v>5.6</v>
       </c>
-      <c r="L39" s="2">
+      <c r="M39" s="2">
         <v>12.4</v>
       </c>
-      <c r="M39" s="2">
+      <c r="N39" s="2">
         <v>0.45700000000000002</v>
       </c>
-      <c r="N39" s="2">
+      <c r="O39" s="2">
         <v>1.8</v>
       </c>
-      <c r="O39" s="2">
+      <c r="P39" s="2">
         <v>5.0999999999999996</v>
       </c>
-      <c r="P39" s="2">
+      <c r="Q39" s="2">
         <v>0.36</v>
       </c>
-      <c r="Q39" s="2">
+      <c r="R39" s="2">
         <v>3.8</v>
       </c>
-      <c r="R39" s="2">
+      <c r="S39" s="2">
         <v>7.3</v>
       </c>
-      <c r="S39" s="2">
+      <c r="T39" s="2">
         <v>0.52400000000000002</v>
       </c>
-      <c r="T39" s="2">
+      <c r="U39" s="2">
         <v>0.53100000000000003</v>
       </c>
-      <c r="U39" s="2">
+      <c r="V39" s="2">
         <v>4</v>
       </c>
-      <c r="V39" s="2">
+      <c r="W39" s="2">
         <v>4.8</v>
       </c>
-      <c r="W39" s="2">
+      <c r="X39" s="2">
         <v>0.84</v>
       </c>
-      <c r="X39" s="2">
+      <c r="Y39" s="2">
         <v>1.2</v>
       </c>
-      <c r="Y39" s="2">
+      <c r="Z39" s="2">
         <v>3.9</v>
       </c>
-      <c r="Z39" s="2">
+      <c r="AA39" s="2">
         <v>5.0999999999999996</v>
       </c>
-      <c r="AA39" s="2">
+      <c r="AB39" s="2">
         <v>2.7</v>
       </c>
-      <c r="AB39" s="2">
+      <c r="AC39" s="2">
         <v>0.5</v>
       </c>
-      <c r="AC39" s="2">
+      <c r="AD39" s="2">
         <v>1.3</v>
       </c>
-      <c r="AD39" s="2">
+      <c r="AE39" s="2">
         <v>0.9</v>
       </c>
-      <c r="AE39" s="2">
+      <c r="AF39" s="2">
         <v>3.2</v>
       </c>
-      <c r="AF39" s="2">
+      <c r="AG39" s="2">
         <v>17.100000000000001</v>
       </c>
     </row>
-    <row r="40" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>57</v>
       </c>
-      <c r="B40" t="s">
+      <c r="B40" s="5">
+        <v>1</v>
+      </c>
+      <c r="C40" t="s">
         <v>7</v>
       </c>
-      <c r="C40">
+      <c r="D40">
         <v>24</v>
       </c>
-      <c r="D40">
+      <c r="E40">
         <v>14</v>
       </c>
-      <c r="E40">
+      <c r="F40">
         <v>3</v>
       </c>
-      <c r="G40" s="2" t="s">
+      <c r="H40" s="2" t="s">
         <v>90</v>
-      </c>
-      <c r="H40" s="2">
-        <v>38</v>
       </c>
       <c r="I40" s="2">
         <v>38</v>
       </c>
       <c r="J40" s="2">
+        <v>38</v>
+      </c>
+      <c r="K40" s="2">
         <v>32.700000000000003</v>
       </c>
-      <c r="K40" s="2">
+      <c r="L40" s="2">
         <v>6.3</v>
       </c>
-      <c r="L40" s="2">
+      <c r="M40" s="2">
         <v>14</v>
       </c>
-      <c r="M40" s="2">
+      <c r="N40" s="2">
         <v>0.44800000000000001</v>
       </c>
-      <c r="N40" s="2">
+      <c r="O40" s="2">
         <v>2.5</v>
       </c>
-      <c r="O40" s="2">
+      <c r="P40" s="2">
         <v>7.5</v>
       </c>
-      <c r="P40" s="2">
+      <c r="Q40" s="2">
         <v>0.33600000000000002</v>
       </c>
-      <c r="Q40" s="2">
+      <c r="R40" s="2">
         <v>3.7</v>
       </c>
-      <c r="R40" s="2">
+      <c r="S40" s="2">
         <v>6.4</v>
       </c>
-      <c r="S40" s="2">
+      <c r="T40" s="2">
         <v>0.57999999999999996</v>
       </c>
-      <c r="T40" s="2">
+      <c r="U40" s="2">
         <v>0.53900000000000003</v>
       </c>
-      <c r="U40" s="2">
+      <c r="V40" s="2">
         <v>1.8</v>
       </c>
-      <c r="V40" s="2">
+      <c r="W40" s="2">
         <v>2</v>
       </c>
-      <c r="W40" s="2">
+      <c r="X40" s="2">
         <v>0.87</v>
       </c>
-      <c r="X40" s="2">
+      <c r="Y40" s="2">
         <v>1</v>
       </c>
-      <c r="Y40" s="2">
+      <c r="Z40" s="2">
         <v>3.5</v>
       </c>
-      <c r="Z40" s="2">
+      <c r="AA40" s="2">
         <v>4.5</v>
       </c>
-      <c r="AA40" s="2">
+      <c r="AB40" s="2">
         <v>5.2</v>
       </c>
-      <c r="AB40" s="2">
+      <c r="AC40" s="2">
         <v>0.8</v>
       </c>
-      <c r="AC40" s="2">
+      <c r="AD40" s="2">
         <v>0.1</v>
       </c>
-      <c r="AD40" s="2">
+      <c r="AE40" s="2">
         <v>1.1000000000000001</v>
       </c>
-      <c r="AE40" s="2">
+      <c r="AF40" s="2">
         <v>1.5</v>
       </c>
-      <c r="AF40" s="2">
+      <c r="AG40" s="2">
         <v>16.8</v>
       </c>
     </row>
-    <row r="41" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>58</v>
       </c>
-      <c r="B41" t="s">
+      <c r="B41" s="5">
+        <v>1</v>
+      </c>
+      <c r="C41" t="s">
         <v>11</v>
       </c>
-      <c r="C41">
+      <c r="D41">
         <v>17</v>
       </c>
-      <c r="D41">
+      <c r="E41">
         <v>22</v>
       </c>
-      <c r="E41">
+      <c r="F41">
         <v>11</v>
       </c>
-      <c r="G41" s="2" t="s">
+      <c r="H41" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="H41" s="2">
+      <c r="I41" s="2">
         <v>39</v>
       </c>
-      <c r="I41" s="2">
+      <c r="J41" s="2">
         <v>34</v>
       </c>
-      <c r="J41" s="2">
+      <c r="K41" s="2">
         <v>31.8</v>
       </c>
-      <c r="K41" s="2">
+      <c r="L41" s="2">
         <v>6.3</v>
       </c>
-      <c r="L41" s="2">
+      <c r="M41" s="2">
         <v>13.5</v>
       </c>
-      <c r="M41" s="2">
+      <c r="N41" s="2">
         <v>0.46800000000000003</v>
       </c>
-      <c r="N41" s="2">
+      <c r="O41" s="2">
         <v>2.2999999999999998</v>
       </c>
-      <c r="O41" s="2">
+      <c r="P41" s="2">
         <v>5.8</v>
       </c>
-      <c r="P41" s="2">
+      <c r="Q41" s="2">
         <v>0.40300000000000002</v>
       </c>
-      <c r="Q41" s="2">
+      <c r="R41" s="2">
         <v>4</v>
       </c>
-      <c r="R41" s="2">
+      <c r="S41" s="2">
         <v>7.7</v>
       </c>
-      <c r="S41" s="2">
+      <c r="T41" s="2">
         <v>0.51700000000000002</v>
       </c>
-      <c r="T41" s="2">
+      <c r="U41" s="2">
         <v>0.55400000000000005</v>
       </c>
-      <c r="U41" s="2">
+      <c r="V41" s="2">
         <v>1.7</v>
       </c>
-      <c r="V41" s="2">
+      <c r="W41" s="2">
         <v>2.2000000000000002</v>
       </c>
-      <c r="W41" s="2">
+      <c r="X41" s="2">
         <v>0.77400000000000002</v>
       </c>
-      <c r="X41" s="2">
+      <c r="Y41" s="2">
         <v>0.8</v>
       </c>
-      <c r="Y41" s="2">
+      <c r="Z41" s="2">
         <v>3.7</v>
       </c>
-      <c r="Z41" s="2">
+      <c r="AA41" s="2">
         <v>4.4000000000000004</v>
       </c>
-      <c r="AA41" s="2">
+      <c r="AB41" s="2">
         <v>5.6</v>
       </c>
-      <c r="AB41" s="2">
+      <c r="AC41" s="2">
         <v>1.5</v>
       </c>
-      <c r="AC41" s="2">
+      <c r="AD41" s="2">
         <v>0.4</v>
       </c>
-      <c r="AD41" s="2">
+      <c r="AE41" s="2">
         <v>2.2999999999999998</v>
       </c>
-      <c r="AE41" s="2">
+      <c r="AF41" s="2">
         <v>2.8</v>
       </c>
-      <c r="AF41" s="2">
+      <c r="AG41" s="2">
         <v>16.600000000000001</v>
       </c>
     </row>
-    <row r="42" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>59</v>
       </c>
-      <c r="B42" t="s">
+      <c r="B42" s="5">
+        <v>1</v>
+      </c>
+      <c r="C42" t="s">
         <v>29</v>
       </c>
-      <c r="C42">
+      <c r="D42">
         <v>24</v>
       </c>
-      <c r="D42">
+      <c r="E42">
         <v>16</v>
       </c>
-      <c r="E42">
+      <c r="F42">
         <v>4</v>
       </c>
-      <c r="F42" t="s">
+      <c r="G42" t="s">
         <v>94</v>
       </c>
-      <c r="G42" s="2" t="s">
+      <c r="H42" s="2" t="s">
         <v>90</v>
-      </c>
-      <c r="H42" s="2">
-        <v>39</v>
       </c>
       <c r="I42" s="2">
         <v>39</v>
       </c>
       <c r="J42" s="2">
+        <v>39</v>
+      </c>
+      <c r="K42" s="2">
         <v>32.5</v>
       </c>
-      <c r="K42" s="2">
+      <c r="L42" s="2">
         <v>5.7</v>
       </c>
-      <c r="L42" s="2">
+      <c r="M42" s="2">
         <v>13.4</v>
       </c>
-      <c r="M42" s="2">
+      <c r="N42" s="2">
         <v>0.42299999999999999</v>
       </c>
-      <c r="N42" s="2">
+      <c r="O42" s="2">
         <v>2.5</v>
       </c>
-      <c r="O42" s="2">
+      <c r="P42" s="2">
         <v>7.1</v>
       </c>
-      <c r="P42" s="2">
+      <c r="Q42" s="2">
         <v>0.35299999999999998</v>
       </c>
-      <c r="Q42" s="2">
+      <c r="R42" s="2">
         <v>3.2</v>
       </c>
-      <c r="R42" s="2">
+      <c r="S42" s="2">
         <v>6.3</v>
       </c>
-      <c r="S42" s="2">
+      <c r="T42" s="2">
         <v>0.502</v>
       </c>
-      <c r="T42" s="2">
+      <c r="U42" s="2">
         <v>0.51600000000000001</v>
       </c>
-      <c r="U42" s="2">
+      <c r="V42" s="2">
         <v>2.6</v>
       </c>
-      <c r="V42" s="2">
+      <c r="W42" s="2">
         <v>3.3</v>
       </c>
-      <c r="W42" s="2">
+      <c r="X42" s="2">
         <v>0.79100000000000004</v>
       </c>
-      <c r="X42" s="2">
+      <c r="Y42" s="2">
         <v>0.5</v>
       </c>
-      <c r="Y42" s="2">
+      <c r="Z42" s="2">
         <v>3.6</v>
       </c>
-      <c r="Z42" s="2">
+      <c r="AA42" s="2">
         <v>4.2</v>
       </c>
-      <c r="AA42" s="2">
+      <c r="AB42" s="2">
         <v>6.3</v>
       </c>
-      <c r="AB42" s="2">
+      <c r="AC42" s="2">
         <v>1.2</v>
       </c>
-      <c r="AC42" s="2">
+      <c r="AD42" s="2">
         <v>0.1</v>
       </c>
-      <c r="AD42" s="2">
+      <c r="AE42" s="2">
         <v>1.7</v>
       </c>
-      <c r="AE42" s="2">
+      <c r="AF42" s="2">
         <v>2.1</v>
       </c>
-      <c r="AF42" s="2">
+      <c r="AG42" s="2">
         <v>16.5</v>
       </c>
-      <c r="AG42" s="2"/>
+      <c r="AH42" s="2"/>
     </row>
-    <row r="43" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>60</v>
       </c>
-      <c r="B43" t="s">
+      <c r="B43" s="5">
+        <v>1</v>
+      </c>
+      <c r="C43" t="s">
         <v>43</v>
       </c>
-      <c r="C43">
+      <c r="D43">
         <v>18</v>
       </c>
-      <c r="D43">
+      <c r="E43">
         <v>20</v>
       </c>
-      <c r="E43">
+      <c r="F43">
         <v>10</v>
       </c>
-      <c r="G43" s="2" t="s">
+      <c r="H43" s="2" t="s">
         <v>91</v>
-      </c>
-      <c r="H43" s="2">
-        <v>37</v>
       </c>
       <c r="I43" s="2">
         <v>37</v>
       </c>
       <c r="J43" s="2">
+        <v>37</v>
+      </c>
+      <c r="K43" s="2">
         <v>30.5</v>
       </c>
-      <c r="K43" s="2">
+      <c r="L43" s="2">
         <v>6.8</v>
       </c>
-      <c r="L43" s="2">
+      <c r="M43" s="2">
         <v>13.5</v>
       </c>
-      <c r="M43" s="2">
+      <c r="N43" s="2">
         <v>0.502</v>
       </c>
-      <c r="N43" s="2">
+      <c r="O43" s="2">
         <v>1.8</v>
       </c>
-      <c r="O43" s="2">
+      <c r="P43" s="2">
         <v>4.8</v>
       </c>
-      <c r="P43" s="2">
+      <c r="Q43" s="2">
         <v>0.38600000000000001</v>
       </c>
-      <c r="Q43" s="2">
+      <c r="R43" s="2">
         <v>4.9000000000000004</v>
       </c>
-      <c r="R43" s="2">
+      <c r="S43" s="2">
         <v>8.6999999999999993</v>
       </c>
-      <c r="S43" s="2">
+      <c r="T43" s="2">
         <v>0.56499999999999995</v>
       </c>
-      <c r="T43" s="2">
+      <c r="U43" s="2">
         <v>0.56999999999999995</v>
       </c>
-      <c r="U43" s="2">
+      <c r="V43" s="2">
         <v>1.1000000000000001</v>
       </c>
-      <c r="V43" s="2">
+      <c r="W43" s="2">
         <v>1.4</v>
       </c>
-      <c r="W43" s="2">
+      <c r="X43" s="2">
         <v>0.79200000000000004</v>
       </c>
-      <c r="X43" s="2">
+      <c r="Y43" s="2">
         <v>2.2000000000000002</v>
       </c>
-      <c r="Y43" s="2">
+      <c r="Z43" s="2">
         <v>7.1</v>
       </c>
-      <c r="Z43" s="2">
+      <c r="AA43" s="2">
         <v>9.3000000000000007</v>
       </c>
-      <c r="AA43" s="2">
+      <c r="AB43" s="2">
         <v>3.6</v>
       </c>
-      <c r="AB43" s="2">
+      <c r="AC43" s="2">
         <v>0.7</v>
       </c>
-      <c r="AC43" s="2">
+      <c r="AD43" s="2">
         <v>0.5</v>
       </c>
-      <c r="AD43" s="2">
+      <c r="AE43" s="2">
         <v>1.5</v>
       </c>
-      <c r="AE43" s="2">
+      <c r="AF43" s="2">
         <v>2</v>
       </c>
-      <c r="AF43" s="2">
+      <c r="AG43" s="2">
         <v>16.5</v>
       </c>
     </row>
-    <row r="44" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>61</v>
       </c>
-      <c r="B44" t="s">
+      <c r="B44" s="5">
+        <v>1</v>
+      </c>
+      <c r="C44" t="s">
         <v>19</v>
       </c>
-      <c r="C44">
+      <c r="D44">
         <v>20</v>
       </c>
-      <c r="D44">
+      <c r="E44">
         <v>19</v>
       </c>
-      <c r="E44">
+      <c r="F44">
         <v>8</v>
       </c>
-      <c r="F44" t="s">
+      <c r="G44" t="s">
         <v>94</v>
       </c>
-      <c r="G44" s="2" t="s">
+      <c r="H44" s="2" t="s">
         <v>91</v>
-      </c>
-      <c r="H44" s="2">
-        <v>31</v>
       </c>
       <c r="I44" s="2">
         <v>31</v>
       </c>
       <c r="J44" s="2">
+        <v>31</v>
+      </c>
+      <c r="K44" s="2">
         <v>30.8</v>
       </c>
-      <c r="K44" s="2">
+      <c r="L44" s="2">
         <v>6</v>
       </c>
-      <c r="L44" s="2">
+      <c r="M44" s="2">
         <v>13.5</v>
       </c>
-      <c r="M44" s="2">
+      <c r="N44" s="2">
         <v>0.44600000000000001</v>
       </c>
-      <c r="N44" s="2">
+      <c r="O44" s="2">
         <v>1.2</v>
       </c>
-      <c r="O44" s="2">
+      <c r="P44" s="2">
         <v>3.9</v>
       </c>
-      <c r="P44" s="2">
+      <c r="Q44" s="2">
         <v>0.317</v>
       </c>
-      <c r="Q44" s="2">
+      <c r="R44" s="2">
         <v>4.8</v>
       </c>
-      <c r="R44" s="2">
+      <c r="S44" s="2">
         <v>9.6</v>
       </c>
-      <c r="S44" s="2">
+      <c r="T44" s="2">
         <v>0.498</v>
       </c>
-      <c r="T44" s="2">
+      <c r="U44" s="2">
         <v>0.49199999999999999</v>
       </c>
-      <c r="U44" s="2">
+      <c r="V44" s="2">
         <v>3.1</v>
       </c>
-      <c r="V44" s="2">
+      <c r="W44" s="2">
         <v>4.0999999999999996</v>
       </c>
-      <c r="W44" s="2">
+      <c r="X44" s="2">
         <v>0.75800000000000001</v>
       </c>
-      <c r="X44" s="2">
+      <c r="Y44" s="2">
         <v>1.6</v>
       </c>
-      <c r="Y44" s="2">
+      <c r="Z44" s="2">
         <v>8.1</v>
       </c>
-      <c r="Z44" s="2">
+      <c r="AA44" s="2">
         <v>9.6999999999999993</v>
       </c>
-      <c r="AA44" s="2">
+      <c r="AB44" s="2">
         <v>2.6</v>
       </c>
-      <c r="AB44" s="2">
+      <c r="AC44" s="2">
         <v>0.9</v>
       </c>
-      <c r="AC44" s="2">
+      <c r="AD44" s="2">
         <v>0.8</v>
       </c>
-      <c r="AD44" s="2">
+      <c r="AE44" s="2">
         <v>1.9</v>
       </c>
-      <c r="AE44" s="2">
+      <c r="AF44" s="2">
         <v>1.7</v>
       </c>
-      <c r="AF44" s="2">
+      <c r="AG44" s="2">
         <v>16.399999999999999</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AF44" xr:uid="{C606AA21-296B-D248-87CD-1A67A00CACCB}"/>
+  <autoFilter ref="A1:AG44" xr:uid="{C606AA21-296B-D248-87CD-1A67A00CACCB}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
